--- a/Indicator_4/Real_data/Blue_Shark_SAtl.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_SAtl.xlsx
@@ -1,22 +1,300 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679DF415-758A-4353-9D0F-F5B50EF49D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Blue_Shark_SAtl</t>
+  </si>
+  <si>
+    <t>E.g. 'Swordfish_Natl'</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>max_age</t>
+  </si>
+  <si>
+    <t>14.184</t>
+  </si>
+  <si>
+    <t>Age to 5% natural survival</t>
+  </si>
+  <si>
+    <t>Life history</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>von Bertalannfy K</t>
+  </si>
+  <si>
+    <t>Linf</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>von Bertalannfy L-infinity (asymptotic length)</t>
+  </si>
+  <si>
+    <t>L50_Linf</t>
+  </si>
+  <si>
+    <t>291.8</t>
+  </si>
+  <si>
+    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+  </si>
+  <si>
+    <t>Total_L5_L50</t>
+  </si>
+  <si>
+    <t>0.423</t>
+  </si>
+  <si>
+    <t>Length at 5% selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Fleet selectivity</t>
+  </si>
+  <si>
+    <t>All fleets combined</t>
+  </si>
+  <si>
+    <t>Total_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.059</t>
+  </si>
+  <si>
+    <t>Length at full selection relative to length at 50% maturity</t>
+  </si>
+  <si>
+    <t>Total_VML</t>
+  </si>
+  <si>
+    <t>0.224</t>
+  </si>
+  <si>
+    <t>Selectivity of maximum length class</t>
+  </si>
+  <si>
+    <t>Fleet_1_L5_L50</t>
+  </si>
+  <si>
+    <t>0.615</t>
+  </si>
+  <si>
+    <t>Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet_1_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.021</t>
+  </si>
+  <si>
+    <t>Fleet_1_VML</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Fleet_2_L5_L50</t>
+  </si>
+  <si>
+    <t>0.445</t>
+  </si>
+  <si>
+    <t>Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_2_LFS_L50</t>
+  </si>
+  <si>
+    <t>0.998</t>
+  </si>
+  <si>
+    <t>Fleet_2_VML</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Fleet_3_L5_L50</t>
+  </si>
+  <si>
+    <t>0.408</t>
+  </si>
+  <si>
+    <t>Fleet 3</t>
+  </si>
+  <si>
+    <t>Fleet_3_LFS_L50</t>
+  </si>
+  <si>
+    <t>1.061</t>
+  </si>
+  <si>
+    <t>Fleet_3_VML</t>
+  </si>
+  <si>
+    <t>0.197</t>
+  </si>
+  <si>
+    <t>Fleet_1_CF</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 1</t>
+  </si>
+  <si>
+    <t>Fleet catch scale</t>
+  </si>
+  <si>
+    <t>Fleet_2_CF</t>
+  </si>
+  <si>
+    <t>0.212</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 2</t>
+  </si>
+  <si>
+    <t>Fleet_3_CF</t>
+  </si>
+  <si>
+    <t>0.719</t>
+  </si>
+  <si>
+    <t>Fraction of all historical catches that were Fleet 3</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Total_catch</t>
+  </si>
+  <si>
+    <t>Total_mean_len</t>
+  </si>
+  <si>
+    <t>Total_mean_age</t>
+  </si>
+  <si>
+    <t>Total_CV_len</t>
+  </si>
+  <si>
+    <t>Total_frac_mat</t>
+  </si>
+  <si>
+    <t>Total_Index</t>
+  </si>
+  <si>
+    <t>Fleet_1_catch</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_1_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_1_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_1_Index</t>
+  </si>
+  <si>
+    <t>Fleet_2_catch</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_2_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_2_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_2_Index</t>
+  </si>
+  <si>
+    <t>Fleet_3_catch</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_mean_age</t>
+  </si>
+  <si>
+    <t>Fleet_3_CV_len</t>
+  </si>
+  <si>
+    <t>Fleet_3_frac_mat</t>
+  </si>
+  <si>
+    <t>Fleet_3_Index</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,13 +342,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -108,7 +394,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -142,6 +428,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -176,9 +463,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -351,656 +639,365 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Blue_Shark_SAtl</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Genus specius</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Billfish</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>North Atlantic</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_age</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>14.184</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Age to 5% natural survival</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>von Bertalannfy K</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L50_Linf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Life history</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>All_L5_L50</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.423</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>All_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.059</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>All_VML</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>0.224</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fleet_1_L5_L50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0.615</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fleet_1_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.021</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fleet_1_VML</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fleet_2_L5_L50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.445</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fleet_2_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0.998</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fleet_2_VML</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fleet_3_L5_L50</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0.408</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Length at 5% selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fleet_3_LFS_L50</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.061</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Length at full selection relative to length at 50% maturity</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Fleet_3_VML</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Selectivity of maximum length class</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Fleet selectivity</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>All_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.636</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>All fleets combined</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Fleet_1_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.572</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Fleet_2_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.494</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Fleet_3_ML_Linf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0.652</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Last historical mean length relative to Linf (e.g. mulen(2024) / Linf)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Fleet catch-length</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fleet_1_CF</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>0.069</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Fleet 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fleet_2_CF</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>0.212</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Fleet 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Fleet_3_CF</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0.719</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fraction of all historical catches that were Fleet 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Fleet catch scale</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Fleet 3</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1009,138 +1006,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Total_catch</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_len</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Total_mean_age</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Total_CV_len</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total_frac_mat</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Index</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_catch</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_len</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_mean_age</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_CV_len</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_frac_mat</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_1_Index</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_catch</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_len</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_mean_age</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_CV_len</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_frac_mat</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_2_Index</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_catch</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_len</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_mean_age</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_CV_len</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_frac_mat</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Fleet_3_Index</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1971</v>
       </c>
@@ -1148,130 +1095,130 @@
         <v>4732.317</v>
       </c>
       <c r="G2">
-        <v>1.683</v>
+        <v>1.6830000000000001</v>
       </c>
       <c r="H2">
-        <v>87.03700000000001</v>
+        <v>87.037000000000006</v>
       </c>
       <c r="N2">
-        <v>1132.36</v>
+        <v>1132.3599999999999</v>
       </c>
       <c r="T2">
         <v>3512.92</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1972</v>
       </c>
       <c r="B3">
-        <v>5267.099</v>
+        <v>5267.0990000000002</v>
       </c>
       <c r="G3">
-        <v>1.412</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="H3">
-        <v>68.386</v>
+        <v>68.385999999999996</v>
       </c>
       <c r="N3">
-        <v>759.703</v>
+        <v>759.70299999999997</v>
       </c>
       <c r="T3">
         <v>4439.01</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1973</v>
       </c>
       <c r="B4">
-        <v>6860.283</v>
+        <v>6860.2830000000004</v>
       </c>
       <c r="G4">
-        <v>1.412</v>
+        <v>1.4119999999999999</v>
       </c>
       <c r="H4">
-        <v>90.99299999999999</v>
+        <v>90.992999999999995</v>
       </c>
       <c r="N4">
         <v>2478.94</v>
       </c>
       <c r="T4">
-        <v>4290.35</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>4290.3500000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1974</v>
       </c>
       <c r="B5">
-        <v>4454.403</v>
+        <v>4454.4030000000002</v>
       </c>
       <c r="G5">
         <v>1.421</v>
       </c>
       <c r="H5">
-        <v>262.805</v>
+        <v>262.80500000000001</v>
       </c>
       <c r="N5">
-        <v>666.008</v>
+        <v>666.00800000000004</v>
       </c>
       <c r="T5">
         <v>3525.59</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1975</v>
       </c>
       <c r="B6">
-        <v>4071.264</v>
+        <v>4071.2640000000001</v>
       </c>
       <c r="G6">
         <v>1.427</v>
       </c>
       <c r="H6">
-        <v>290.499</v>
+        <v>290.49900000000002</v>
       </c>
       <c r="N6">
-        <v>643.085</v>
+        <v>643.08500000000004</v>
       </c>
       <c r="T6">
         <v>3137.68</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1976</v>
       </c>
       <c r="B7">
-        <v>4506.506</v>
+        <v>4506.5060000000003</v>
       </c>
       <c r="G7">
         <v>1.429</v>
       </c>
       <c r="H7">
-        <v>206.288</v>
+        <v>206.28800000000001</v>
       </c>
       <c r="N7">
-        <v>488.868</v>
+        <v>488.86799999999999</v>
       </c>
       <c r="T7">
         <v>3811.35</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1977</v>
       </c>
       <c r="B8">
-        <v>9515.505999999999</v>
+        <v>9515.5059999999994</v>
       </c>
       <c r="G8">
-        <v>1.438</v>
+        <v>1.4379999999999999</v>
       </c>
       <c r="H8">
-        <v>217.026</v>
+        <v>217.02600000000001</v>
       </c>
       <c r="N8">
         <v>5764.68</v>
@@ -1280,7 +1227,7 @@
         <v>3533.8</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1978</v>
       </c>
@@ -1288,10 +1235,10 @@
         <v>10503.758</v>
       </c>
       <c r="G9">
-        <v>1.449</v>
+        <v>1.4490000000000001</v>
       </c>
       <c r="H9">
-        <v>207.418</v>
+        <v>207.41800000000001</v>
       </c>
       <c r="N9">
         <v>6800.44</v>
@@ -1300,7 +1247,7 @@
         <v>3495.9</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1979</v>
       </c>
@@ -1308,7 +1255,7 @@
         <v>11262.82</v>
       </c>
       <c r="G10">
-        <v>1.459</v>
+        <v>1.4590000000000001</v>
       </c>
       <c r="H10">
         <v>293.89</v>
@@ -1320,7 +1267,7 @@
         <v>3341.26</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1980</v>
       </c>
@@ -1331,36 +1278,36 @@
         <v>1.452</v>
       </c>
       <c r="H11">
-        <v>892.408</v>
+        <v>892.40800000000002</v>
       </c>
       <c r="N11">
-        <v>8655.379999999999</v>
+        <v>8655.3799999999992</v>
       </c>
       <c r="T11">
         <v>3089.75</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1981</v>
       </c>
       <c r="B12">
-        <v>7923.985</v>
+        <v>7923.9849999999997</v>
       </c>
       <c r="G12">
-        <v>1.441</v>
+        <v>1.4410000000000001</v>
       </c>
       <c r="H12">
-        <v>369.623</v>
+        <v>369.62299999999999</v>
       </c>
       <c r="N12">
         <v>4441.91</v>
       </c>
       <c r="T12">
-        <v>3112.452</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>3112.4520000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1982</v>
       </c>
@@ -1380,12 +1327,12 @@
         <v>3420.895</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1983</v>
       </c>
       <c r="B14">
-        <v>5949.688</v>
+        <v>5949.6880000000001</v>
       </c>
       <c r="G14">
         <v>1.409</v>
@@ -1397,21 +1344,21 @@
         <v>2813.28</v>
       </c>
       <c r="T14">
-        <v>2695.008</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>2695.0079999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1984</v>
       </c>
       <c r="B15">
-        <v>9958.816999999999</v>
+        <v>9958.8169999999991</v>
       </c>
       <c r="G15">
-        <v>1.408</v>
+        <v>1.4079999999999999</v>
       </c>
       <c r="H15">
-        <v>263.936</v>
+        <v>263.93599999999998</v>
       </c>
       <c r="N15">
         <v>7601.39</v>
@@ -1420,18 +1367,18 @@
         <v>2093.491</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1985</v>
       </c>
       <c r="B16">
-        <v>8500.835999999999</v>
+        <v>8500.8359999999993</v>
       </c>
       <c r="G16">
         <v>1.389</v>
       </c>
       <c r="H16">
-        <v>317.627</v>
+        <v>317.62700000000001</v>
       </c>
       <c r="N16">
         <v>6155.67</v>
@@ -1440,7 +1387,7 @@
         <v>2027.539</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1986</v>
       </c>
@@ -1448,7 +1395,7 @@
         <v>12003.017</v>
       </c>
       <c r="G17">
-        <v>1.396</v>
+        <v>1.3959999999999999</v>
       </c>
       <c r="H17">
         <v>425.01</v>
@@ -1457,81 +1404,81 @@
         <v>7716.97</v>
       </c>
       <c r="T17">
-        <v>3861.037</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>3861.0369999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1987</v>
       </c>
       <c r="B18">
-        <v>9586.587</v>
+        <v>9586.5869999999995</v>
       </c>
       <c r="G18">
         <v>1.391</v>
       </c>
       <c r="H18">
-        <v>535.2190000000001</v>
+        <v>535.21900000000005</v>
       </c>
       <c r="N18">
         <v>4706.75</v>
       </c>
       <c r="T18">
-        <v>4344.618</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>4344.6180000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1988</v>
       </c>
       <c r="B19">
-        <v>16927.942</v>
+        <v>16927.941999999999</v>
       </c>
       <c r="G19">
         <v>1.391</v>
       </c>
       <c r="H19">
-        <v>656.731</v>
+        <v>656.73099999999999</v>
       </c>
       <c r="N19">
         <v>7016.24</v>
       </c>
       <c r="T19">
-        <v>9254.971</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>9254.9709999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1989</v>
       </c>
       <c r="B20">
-        <v>21996.896</v>
+        <v>21996.896000000001</v>
       </c>
       <c r="G20">
         <v>1.379</v>
       </c>
       <c r="H20">
-        <v>660.122</v>
+        <v>660.12199999999996</v>
       </c>
       <c r="N20">
         <v>6806.85</v>
       </c>
       <c r="T20">
-        <v>14529.924</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>14529.924000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1990</v>
       </c>
       <c r="B21">
-        <v>25184.943</v>
+        <v>25184.942999999999</v>
       </c>
       <c r="G21">
         <v>1.375</v>
       </c>
       <c r="H21">
-        <v>958.533</v>
+        <v>958.53300000000002</v>
       </c>
       <c r="N21">
         <v>8058.33</v>
@@ -1540,18 +1487,18 @@
         <v>16168.08</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1991</v>
       </c>
       <c r="B22">
-        <v>21219.332</v>
+        <v>21219.331999999999</v>
       </c>
       <c r="G22">
         <v>1.345</v>
       </c>
       <c r="H22">
-        <v>741.5069999999999</v>
+        <v>741.50699999999995</v>
       </c>
       <c r="N22">
         <v>6559.97</v>
@@ -1560,30 +1507,30 @@
         <v>13917.855</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1992</v>
       </c>
       <c r="B23">
-        <v>23229.132</v>
+        <v>23229.132000000001</v>
       </c>
       <c r="G23">
-        <v>1.295</v>
+        <v>1.2949999999999999</v>
       </c>
       <c r="H23">
         <v>1474.54</v>
       </c>
       <c r="N23">
-        <v>4748.23</v>
+        <v>4748.2299999999996</v>
       </c>
       <c r="T23">
-        <v>17006.362</v>
+        <v>17006.362000000001</v>
       </c>
       <c r="Y23">
-        <v>1.414</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>1.4139999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -1591,16 +1538,16 @@
         <v>23127.734</v>
       </c>
       <c r="C24">
-        <v>201.469</v>
+        <v>201.46899999999999</v>
       </c>
       <c r="E24">
         <v>0.16</v>
       </c>
       <c r="F24">
-        <v>0.8090000000000001</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="G24">
-        <v>1.239</v>
+        <v>1.2390000000000001</v>
       </c>
       <c r="H24">
         <v>1137.69</v>
@@ -1609,63 +1556,63 @@
         <v>7833.96</v>
       </c>
       <c r="T24">
-        <v>14156.084</v>
+        <v>14156.084000000001</v>
       </c>
       <c r="U24">
-        <v>201.469</v>
+        <v>201.46899999999999</v>
       </c>
       <c r="W24">
         <v>0.16</v>
       </c>
       <c r="X24">
-        <v>0.8090000000000001</v>
+        <v>0.80900000000000005</v>
       </c>
       <c r="Y24">
-        <v>0.9379999999999999</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>0.93799999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1994</v>
       </c>
       <c r="B25">
-        <v>26721.239</v>
+        <v>26721.239000000001</v>
       </c>
       <c r="C25">
-        <v>199.877</v>
+        <v>199.87700000000001</v>
       </c>
       <c r="E25">
         <v>0.13</v>
       </c>
       <c r="F25">
-        <v>0.789</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="G25">
         <v>1.2</v>
       </c>
       <c r="H25">
-        <v>887.8869999999999</v>
+        <v>887.88699999999994</v>
       </c>
       <c r="N25">
         <v>7658.81</v>
       </c>
       <c r="T25">
-        <v>18174.542</v>
+        <v>18174.542000000001</v>
       </c>
       <c r="U25">
-        <v>199.877</v>
+        <v>199.87700000000001</v>
       </c>
       <c r="W25">
         <v>0.13</v>
       </c>
       <c r="X25">
-        <v>0.789</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="Y25">
-        <v>0.904</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>0.90400000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1995</v>
       </c>
@@ -1676,101 +1623,101 @@
         <v>199.428</v>
       </c>
       <c r="E26">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="F26">
-        <v>0.764</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="G26">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="H26">
-        <v>1113.39</v>
+        <v>1113.3900000000001</v>
       </c>
       <c r="N26">
         <v>5555.57</v>
       </c>
       <c r="T26">
-        <v>22140.452</v>
+        <v>22140.452000000001</v>
       </c>
       <c r="U26">
         <v>199.428</v>
       </c>
       <c r="W26">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="X26">
-        <v>0.764</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="Y26">
-        <v>0.838</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>0.83799999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1996</v>
       </c>
       <c r="B27">
-        <v>30158.112</v>
+        <v>30158.112000000001</v>
       </c>
       <c r="C27">
-        <v>157.611</v>
+        <v>157.61099999999999</v>
       </c>
       <c r="E27">
-        <v>0.196</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="F27">
-        <v>0.357</v>
+        <v>0.35699999999999998</v>
       </c>
       <c r="G27">
-        <v>1.124</v>
+        <v>1.1240000000000001</v>
       </c>
       <c r="H27">
         <v>1069.31</v>
       </c>
       <c r="N27">
-        <v>4851.81</v>
+        <v>4851.8100000000004</v>
       </c>
       <c r="O27">
-        <v>119.118</v>
+        <v>119.11799999999999</v>
       </c>
       <c r="Q27">
-        <v>0.275</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="R27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>24236.992</v>
+        <v>24236.991999999998</v>
       </c>
       <c r="U27">
-        <v>196.105</v>
+        <v>196.10499999999999</v>
       </c>
       <c r="W27">
-        <v>0.116</v>
+        <v>0.11600000000000001</v>
       </c>
       <c r="X27">
-        <v>0.713</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="Y27">
-        <v>0.736</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>0.73599999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1997</v>
       </c>
       <c r="B28">
-        <v>23105.818</v>
+        <v>23105.817999999999</v>
       </c>
       <c r="C28">
-        <v>200.972</v>
+        <v>200.97200000000001</v>
       </c>
       <c r="E28">
-        <v>0.101</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F28">
-        <v>0.8110000000000001</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="G28">
         <v>1.056</v>
@@ -1779,16 +1726,16 @@
         <v>2317.21</v>
       </c>
       <c r="N28">
-        <v>4396.52</v>
+        <v>4396.5200000000004</v>
       </c>
       <c r="O28">
-        <v>202.475</v>
+        <v>202.47499999999999</v>
       </c>
       <c r="Q28">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="R28">
-        <v>0.828</v>
+        <v>0.82799999999999996</v>
       </c>
       <c r="T28">
         <v>16392.088</v>
@@ -1800,13 +1747,13 @@
         <v>0.104</v>
       </c>
       <c r="X28">
-        <v>0.794</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="Y28">
-        <v>0.775</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>0.77500000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1998</v>
       </c>
@@ -1814,45 +1761,45 @@
         <v>21501.678</v>
       </c>
       <c r="C29">
-        <v>203.531</v>
+        <v>203.53100000000001</v>
       </c>
       <c r="E29">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="F29">
-        <v>0.775</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="G29">
-        <v>0.954</v>
+        <v>0.95399999999999996</v>
       </c>
       <c r="H29">
-        <v>2172.53</v>
+        <v>2172.5300000000002</v>
       </c>
       <c r="N29">
         <v>3720.34</v>
       </c>
       <c r="T29">
-        <v>15608.808</v>
+        <v>15608.808000000001</v>
       </c>
       <c r="U29">
-        <v>203.531</v>
+        <v>203.53100000000001</v>
       </c>
       <c r="W29">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="X29">
-        <v>0.775</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="Y29">
         <v>0.84</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1999</v>
       </c>
       <c r="B30">
-        <v>23001.219</v>
+        <v>23001.219000000001</v>
       </c>
       <c r="C30">
         <v>185.94</v>
@@ -1861,10 +1808,10 @@
         <v>0.222</v>
       </c>
       <c r="F30">
-        <v>0.639</v>
+        <v>0.63900000000000001</v>
       </c>
       <c r="G30">
-        <v>0.838</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="H30">
         <v>2668.18</v>
@@ -1873,16 +1820,16 @@
         <v>3133.5</v>
       </c>
       <c r="O30">
-        <v>142.975</v>
+        <v>142.97499999999999</v>
       </c>
       <c r="Q30">
-        <v>0.353</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="R30">
         <v>0.24</v>
       </c>
       <c r="T30">
-        <v>17199.539</v>
+        <v>17199.539000000001</v>
       </c>
       <c r="U30">
         <v>207.422</v>
@@ -1891,30 +1838,30 @@
         <v>0.156</v>
       </c>
       <c r="X30">
-        <v>0.838</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="Y30">
-        <v>0.802</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>0.80200000000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2000</v>
       </c>
       <c r="B31">
-        <v>23089.132</v>
+        <v>23089.132000000001</v>
       </c>
       <c r="C31">
-        <v>160.418</v>
+        <v>160.41800000000001</v>
       </c>
       <c r="E31">
-        <v>0.228</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="F31">
-        <v>0.355</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="G31">
-        <v>0.759</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="H31">
         <v>1682.5</v>
@@ -1923,48 +1870,48 @@
         <v>2950.82</v>
       </c>
       <c r="O31">
-        <v>132.598</v>
+        <v>132.59800000000001</v>
       </c>
       <c r="Q31">
-        <v>0.268</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="R31">
-        <v>0.039</v>
+        <v>3.9E-2</v>
       </c>
       <c r="T31">
-        <v>18455.812</v>
+        <v>18455.812000000002</v>
       </c>
       <c r="U31">
-        <v>174.329</v>
+        <v>174.32900000000001</v>
       </c>
       <c r="W31">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="X31">
-        <v>0.513</v>
+        <v>0.51300000000000001</v>
       </c>
       <c r="Y31">
-        <v>0.828</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>0.82799999999999996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2001</v>
       </c>
       <c r="B32">
-        <v>20808.508</v>
+        <v>20808.508000000002</v>
       </c>
       <c r="C32">
-        <v>176.605</v>
+        <v>176.60499999999999</v>
       </c>
       <c r="E32">
-        <v>0.206</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="F32">
         <v>0.52</v>
       </c>
       <c r="G32">
-        <v>0.705</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="H32">
         <v>2173.4</v>
@@ -1973,16 +1920,16 @@
         <v>1666.67</v>
       </c>
       <c r="O32">
-        <v>166.014</v>
+        <v>166.01400000000001</v>
       </c>
       <c r="Q32">
         <v>0.311</v>
       </c>
       <c r="R32">
-        <v>0.419</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="T32">
-        <v>16968.438</v>
+        <v>16968.437999999998</v>
       </c>
       <c r="U32">
         <v>181.9</v>
@@ -1991,30 +1938,30 @@
         <v>0.154</v>
       </c>
       <c r="X32">
-        <v>0.571</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="Y32">
-        <v>0.804</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>0.80400000000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2002</v>
       </c>
       <c r="B33">
-        <v>22166.301</v>
+        <v>22166.300999999999</v>
       </c>
       <c r="C33">
         <v>173.483</v>
       </c>
       <c r="E33">
-        <v>0.209</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="F33">
-        <v>0.403</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="G33">
-        <v>0.658</v>
+        <v>0.65800000000000003</v>
       </c>
       <c r="H33">
         <v>1970.5</v>
@@ -2023,16 +1970,16 @@
         <v>1446.59</v>
       </c>
       <c r="O33">
-        <v>172.807</v>
+        <v>172.80699999999999</v>
       </c>
       <c r="Q33">
-        <v>0.206</v>
+        <v>0.20599999999999999</v>
       </c>
       <c r="R33">
-        <v>0.399</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="T33">
-        <v>18749.211</v>
+        <v>18749.210999999999</v>
       </c>
       <c r="U33">
         <v>173.82</v>
@@ -2041,39 +1988,39 @@
         <v>0.21</v>
       </c>
       <c r="X33">
-        <v>0.406</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="Y33">
-        <v>0.779</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>0.77900000000000003</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2003</v>
       </c>
       <c r="B34">
-        <v>26719.467</v>
+        <v>26719.467000000001</v>
       </c>
       <c r="C34">
-        <v>171.051</v>
+        <v>171.05099999999999</v>
       </c>
       <c r="E34">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="F34">
         <v>0.378</v>
       </c>
       <c r="G34">
-        <v>0.611</v>
+        <v>0.61099999999999999</v>
       </c>
       <c r="H34">
-        <v>2165.76</v>
+        <v>2165.7600000000002</v>
       </c>
       <c r="N34">
         <v>5469.22</v>
       </c>
       <c r="O34">
-        <v>176.701</v>
+        <v>176.70099999999999</v>
       </c>
       <c r="Q34">
         <v>0.223</v>
@@ -2082,39 +2029,39 @@
         <v>0.442</v>
       </c>
       <c r="T34">
-        <v>19084.487</v>
+        <v>19084.487000000001</v>
       </c>
       <c r="U34">
-        <v>168.225</v>
+        <v>168.22499999999999</v>
       </c>
       <c r="W34">
-        <v>0.207</v>
+        <v>0.20699999999999999</v>
       </c>
       <c r="X34">
-        <v>0.346</v>
+        <v>0.34599999999999997</v>
       </c>
       <c r="Y34">
-        <v>0.825</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>0.82499999999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2004</v>
       </c>
       <c r="B35">
-        <v>22402.671</v>
+        <v>22402.670999999998</v>
       </c>
       <c r="C35">
-        <v>165.254</v>
+        <v>165.25399999999999</v>
       </c>
       <c r="E35">
         <v>0.246</v>
       </c>
       <c r="F35">
-        <v>0.345</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="G35">
-        <v>0.575</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="H35">
         <v>1667.36</v>
@@ -2123,39 +2070,39 @@
         <v>2680.3</v>
       </c>
       <c r="T35">
-        <v>18055.011</v>
+        <v>18055.010999999999</v>
       </c>
       <c r="U35">
-        <v>165.254</v>
+        <v>165.25399999999999</v>
       </c>
       <c r="W35">
         <v>0.246</v>
       </c>
       <c r="X35">
-        <v>0.345</v>
+        <v>0.34499999999999997</v>
       </c>
       <c r="Y35">
-        <v>0.766</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>0.76600000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2005</v>
       </c>
       <c r="B36">
-        <v>26593.075</v>
+        <v>26593.075000000001</v>
       </c>
       <c r="C36">
-        <v>180.094</v>
+        <v>180.09399999999999</v>
       </c>
       <c r="E36">
-        <v>0.213</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="F36">
         <v>0.49</v>
       </c>
       <c r="G36">
-        <v>0.5570000000000001</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="H36">
         <v>2523.27</v>
@@ -2176,28 +2123,28 @@
         <v>146.846</v>
       </c>
       <c r="Q36">
-        <v>0.257</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="R36">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="T36">
-        <v>22409.575</v>
+        <v>22409.575000000001</v>
       </c>
       <c r="U36">
         <v>189.77</v>
       </c>
       <c r="W36">
-        <v>0.203</v>
+        <v>0.20300000000000001</v>
       </c>
       <c r="X36">
-        <v>0.594</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="Y36">
-        <v>0.842</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>0.84199999999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2006</v>
       </c>
@@ -2205,40 +2152,40 @@
         <v>24446.04</v>
       </c>
       <c r="C37">
-        <v>184.723</v>
+        <v>184.72300000000001</v>
       </c>
       <c r="E37">
         <v>0.185</v>
       </c>
       <c r="F37">
-        <v>0.548</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="G37">
-        <v>0.543</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="H37">
         <v>2591.33</v>
       </c>
       <c r="I37">
-        <v>185.782</v>
+        <v>185.78200000000001</v>
       </c>
       <c r="K37">
         <v>0.189</v>
       </c>
       <c r="L37">
-        <v>0.458</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="N37">
         <v>3281.84</v>
       </c>
       <c r="O37">
-        <v>167.576</v>
+        <v>167.57599999999999</v>
       </c>
       <c r="Q37">
-        <v>0.232</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="R37">
-        <v>0.424</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="T37">
         <v>18572.87</v>
@@ -2247,16 +2194,16 @@
         <v>187.941</v>
       </c>
       <c r="W37">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="X37">
-        <v>0.591</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="Y37">
-        <v>0.886</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>0.88600000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2007</v>
       </c>
@@ -2264,16 +2211,16 @@
         <v>26571.555</v>
       </c>
       <c r="C38">
-        <v>165.689</v>
+        <v>165.68899999999999</v>
       </c>
       <c r="E38">
-        <v>0.227</v>
+        <v>0.22700000000000001</v>
       </c>
       <c r="F38">
-        <v>0.291</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="G38">
-        <v>0.542</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="H38">
         <v>2645.28</v>
@@ -2282,31 +2229,31 @@
         <v>153.267</v>
       </c>
       <c r="K38">
-        <v>0.225</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="L38">
-        <v>0.195</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="N38">
         <v>3653.3</v>
       </c>
       <c r="T38">
-        <v>20272.975</v>
+        <v>20272.974999999999</v>
       </c>
       <c r="U38">
-        <v>168.794</v>
+        <v>168.79400000000001</v>
       </c>
       <c r="W38">
-        <v>0.228</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="X38">
         <v>0.315</v>
       </c>
       <c r="Y38">
-        <v>0.909</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>0.90900000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2008</v>
       </c>
@@ -2314,31 +2261,31 @@
         <v>26841.428</v>
       </c>
       <c r="C39">
-        <v>190.377</v>
+        <v>190.37700000000001</v>
       </c>
       <c r="E39">
-        <v>0.179</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="F39">
-        <v>0.611</v>
+        <v>0.61099999999999999</v>
       </c>
       <c r="G39">
-        <v>0.518</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="H39">
         <v>2012.58</v>
       </c>
       <c r="I39">
-        <v>214.885</v>
+        <v>214.88499999999999</v>
       </c>
       <c r="K39">
-        <v>0.165</v>
+        <v>0.16500000000000001</v>
       </c>
       <c r="L39">
-        <v>0.858</v>
+        <v>0.85799999999999998</v>
       </c>
       <c r="M39">
-        <v>0.793</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="N39">
         <v>5521.34</v>
@@ -2347,16 +2294,16 @@
         <v>188.6</v>
       </c>
       <c r="Q39">
-        <v>0.167</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="R39">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S39">
-        <v>1.019</v>
+        <v>1.0189999999999999</v>
       </c>
       <c r="T39">
-        <v>19307.508</v>
+        <v>19307.508000000002</v>
       </c>
       <c r="U39">
         <v>185.83</v>
@@ -2365,13 +2312,13 @@
         <v>0.184</v>
       </c>
       <c r="X39">
-        <v>0.5679999999999999</v>
+        <v>0.56799999999999995</v>
       </c>
       <c r="Y39">
-        <v>1.009</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>1.0089999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2009</v>
       </c>
@@ -2379,10 +2326,10 @@
         <v>26421.572</v>
       </c>
       <c r="C40">
-        <v>180.854</v>
+        <v>180.85400000000001</v>
       </c>
       <c r="E40">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="F40">
         <v>0.502</v>
@@ -2394,19 +2341,19 @@
         <v>1273.5</v>
       </c>
       <c r="M40">
-        <v>0.838</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="N40">
         <v>3768</v>
       </c>
       <c r="O40">
-        <v>170.522</v>
+        <v>170.52199999999999</v>
       </c>
       <c r="Q40">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="R40">
-        <v>0.299</v>
+        <v>0.29899999999999999</v>
       </c>
       <c r="S40">
         <v>0.92</v>
@@ -2415,72 +2362,72 @@
         <v>21380.072</v>
       </c>
       <c r="U40">
-        <v>183.437</v>
+        <v>183.43700000000001</v>
       </c>
       <c r="W40">
-        <v>0.162</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="X40">
-        <v>0.553</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="Y40">
         <v>0.96</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2010</v>
       </c>
       <c r="B41">
-        <v>31973.757</v>
+        <v>31973.757000000001</v>
       </c>
       <c r="C41">
-        <v>175.573</v>
+        <v>175.57300000000001</v>
       </c>
       <c r="E41">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="F41">
-        <v>0.403</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="G41">
-        <v>0.489</v>
+        <v>0.48899999999999999</v>
       </c>
       <c r="H41">
         <v>1500.5</v>
       </c>
       <c r="I41">
-        <v>205.528</v>
+        <v>205.52799999999999</v>
       </c>
       <c r="K41">
-        <v>0.172</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="L41">
-        <v>0.6879999999999999</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="M41">
-        <v>0.756</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="N41">
         <v>5335.59</v>
       </c>
       <c r="O41">
-        <v>158.729</v>
+        <v>158.72900000000001</v>
       </c>
       <c r="Q41">
         <v>0.11</v>
       </c>
       <c r="R41">
-        <v>0.034</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="S41">
         <v>1.264</v>
       </c>
       <c r="T41">
-        <v>25137.667</v>
+        <v>25137.667000000001</v>
       </c>
       <c r="U41">
-        <v>172.951</v>
+        <v>172.95099999999999</v>
       </c>
       <c r="W41">
         <v>0.185</v>
@@ -2489,24 +2436,24 @@
         <v>0.42</v>
       </c>
       <c r="Y41">
-        <v>1.162</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>1.1619999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2011</v>
       </c>
       <c r="B42">
-        <v>37684.956</v>
+        <v>37684.955999999998</v>
       </c>
       <c r="C42">
-        <v>177.639</v>
+        <v>177.63900000000001</v>
       </c>
       <c r="E42">
-        <v>0.178</v>
+        <v>0.17799999999999999</v>
       </c>
       <c r="F42">
-        <v>0.488</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G42">
         <v>0.48</v>
@@ -2527,33 +2474,33 @@
         <v>0.128</v>
       </c>
       <c r="R42">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="S42">
         <v>1.294</v>
       </c>
       <c r="T42">
-        <v>31463.256</v>
+        <v>31463.256000000001</v>
       </c>
       <c r="U42">
-        <v>180.492</v>
+        <v>180.49199999999999</v>
       </c>
       <c r="W42">
         <v>0.187</v>
       </c>
       <c r="X42">
-        <v>0.553</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="Y42">
-        <v>0.921</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>0.92100000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2012</v>
       </c>
       <c r="B43">
-        <v>27734.505</v>
+        <v>27734.505000000001</v>
       </c>
       <c r="C43">
         <v>173.8</v>
@@ -2562,49 +2509,49 @@
         <v>0.161</v>
       </c>
       <c r="F43">
-        <v>0.396</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="G43">
-        <v>0.477</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="H43">
         <v>1607.26</v>
       </c>
       <c r="M43">
-        <v>1.455</v>
+        <v>1.4550000000000001</v>
       </c>
       <c r="N43">
-        <v>4447.36</v>
+        <v>4447.3599999999997</v>
       </c>
       <c r="O43">
-        <v>168.942</v>
+        <v>168.94200000000001</v>
       </c>
       <c r="Q43">
-        <v>0.235</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="R43">
-        <v>0.327</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="S43">
         <v>1.004</v>
       </c>
       <c r="T43">
-        <v>21679.885</v>
+        <v>21679.884999999998</v>
       </c>
       <c r="U43">
-        <v>174.771</v>
+        <v>174.77099999999999</v>
       </c>
       <c r="W43">
-        <v>0.147</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="X43">
         <v>0.41</v>
       </c>
       <c r="Y43">
-        <v>1.191</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>1.1910000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2013</v>
       </c>
@@ -2612,16 +2559,16 @@
         <v>20799.125</v>
       </c>
       <c r="C44">
-        <v>175.574</v>
+        <v>175.57400000000001</v>
       </c>
       <c r="E44">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="F44">
         <v>0.43</v>
       </c>
       <c r="G44">
-        <v>0.469</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="H44">
         <v>1008.13</v>
@@ -2633,57 +2580,57 @@
         <v>3509.4</v>
       </c>
       <c r="O44">
-        <v>169.448</v>
+        <v>169.44800000000001</v>
       </c>
       <c r="Q44">
-        <v>0.212</v>
+        <v>0.21199999999999999</v>
       </c>
       <c r="R44">
-        <v>0.355</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="S44">
         <v>1.081</v>
       </c>
       <c r="T44">
-        <v>16281.595</v>
+        <v>16281.594999999999</v>
       </c>
       <c r="U44">
-        <v>176.799</v>
+        <v>176.79900000000001</v>
       </c>
       <c r="W44">
         <v>0.154</v>
       </c>
       <c r="X44">
-        <v>0.445</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="Y44">
         <v>1.214</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2014</v>
       </c>
       <c r="B45">
-        <v>26252.8</v>
+        <v>26252.799999999999</v>
       </c>
       <c r="C45">
-        <v>178.349</v>
+        <v>178.34899999999999</v>
       </c>
       <c r="E45">
         <v>0.156</v>
       </c>
       <c r="F45">
-        <v>0.455</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="G45">
-        <v>0.444</v>
+        <v>0.44400000000000001</v>
       </c>
       <c r="H45">
         <v>2551.41</v>
       </c>
       <c r="M45">
-        <v>0.857</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="N45">
         <v>3232</v>
@@ -2695,7 +2642,7 @@
         <v>0.185</v>
       </c>
       <c r="R45">
-        <v>0.548</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="S45">
         <v>1.157</v>
@@ -2707,7 +2654,7 @@
         <v>176.928</v>
       </c>
       <c r="W45">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="X45">
         <v>0.432</v>
@@ -2716,7 +2663,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2015</v>
       </c>
@@ -2724,34 +2671,34 @@
         <v>22498.5</v>
       </c>
       <c r="C46">
-        <v>177.353</v>
+        <v>177.35300000000001</v>
       </c>
       <c r="E46">
-        <v>0.136</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="F46">
-        <v>0.508</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="G46">
-        <v>0.467</v>
+        <v>0.46700000000000003</v>
       </c>
       <c r="H46">
-        <v>2420.47</v>
+        <v>2420.4699999999998</v>
       </c>
       <c r="M46">
-        <v>1.096</v>
+        <v>1.0960000000000001</v>
       </c>
       <c r="N46">
         <v>2277.42</v>
       </c>
       <c r="O46">
-        <v>159.212</v>
+        <v>159.21199999999999</v>
       </c>
       <c r="Q46">
-        <v>0.202</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="R46">
-        <v>0.181</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="S46">
         <v>0.89</v>
@@ -2760,7 +2707,7 @@
         <v>17800.61</v>
       </c>
       <c r="U46">
-        <v>181.889</v>
+        <v>181.88900000000001</v>
       </c>
       <c r="W46">
         <v>0.12</v>
@@ -2772,7 +2719,7 @@
         <v>1.111</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2016</v>
       </c>
@@ -2789,28 +2736,28 @@
         <v>0.374</v>
       </c>
       <c r="G47">
-        <v>0.518</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="H47">
         <v>1334.3</v>
       </c>
       <c r="M47">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="N47">
-        <v>2127.3</v>
+        <v>2127.3000000000002</v>
       </c>
       <c r="O47">
-        <v>155.516</v>
+        <v>155.51599999999999</v>
       </c>
       <c r="Q47">
-        <v>0.235</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="R47">
         <v>0.192</v>
       </c>
       <c r="S47">
-        <v>0.928</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="T47">
         <v>21955.08</v>
@@ -2819,16 +2766,16 @@
         <v>174.209</v>
       </c>
       <c r="W47">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X47">
-        <v>0.419</v>
+        <v>0.41899999999999998</v>
       </c>
       <c r="Y47">
         <v>1.486</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2017</v>
       </c>
@@ -2842,25 +2789,25 @@
         <v>0.182</v>
       </c>
       <c r="F48">
-        <v>0.454</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="G48">
-        <v>0.545</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H48">
-        <v>2176.72</v>
+        <v>2176.7199999999998</v>
       </c>
       <c r="I48">
-        <v>181.026</v>
+        <v>181.02600000000001</v>
       </c>
       <c r="K48">
-        <v>0.149</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="L48">
         <v>0.41</v>
       </c>
       <c r="M48">
-        <v>0.9389999999999999</v>
+        <v>0.93899999999999995</v>
       </c>
       <c r="N48">
         <v>3111.65</v>
@@ -2869,13 +2816,13 @@
         <v>167.25</v>
       </c>
       <c r="Q48">
-        <v>0.283</v>
+        <v>0.28299999999999997</v>
       </c>
       <c r="R48">
-        <v>0.471</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="S48">
-        <v>0.928</v>
+        <v>0.92800000000000005</v>
       </c>
       <c r="T48">
         <v>23266.52</v>
@@ -2884,39 +2831,39 @@
         <v>174.476</v>
       </c>
       <c r="W48">
-        <v>0.171</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="X48">
-        <v>0.459</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="Y48">
-        <v>1.102</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>1.1020000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2018</v>
       </c>
       <c r="B49">
-        <v>34513.98</v>
+        <v>34513.980000000003</v>
       </c>
       <c r="C49">
-        <v>177.365</v>
+        <v>177.36500000000001</v>
       </c>
       <c r="E49">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="F49">
-        <v>0.514</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="G49">
-        <v>0.5659999999999999</v>
+        <v>0.56599999999999995</v>
       </c>
       <c r="H49">
         <v>3010.73</v>
       </c>
       <c r="I49">
-        <v>177.627</v>
+        <v>177.62700000000001</v>
       </c>
       <c r="K49">
         <v>0.125</v>
@@ -2925,48 +2872,48 @@
         <v>0.374</v>
       </c>
       <c r="M49">
-        <v>1.142</v>
+        <v>1.1419999999999999</v>
       </c>
       <c r="N49">
         <v>3495.36</v>
       </c>
       <c r="O49">
-        <v>182.635</v>
+        <v>182.63499999999999</v>
       </c>
       <c r="Q49">
-        <v>0.208</v>
+        <v>0.20799999999999999</v>
       </c>
       <c r="R49">
-        <v>0.614</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="S49">
-        <v>0.9360000000000001</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="T49">
         <v>28007.89</v>
       </c>
       <c r="U49">
-        <v>176.443</v>
+        <v>176.44300000000001</v>
       </c>
       <c r="W49">
-        <v>0.166</v>
+        <v>0.16600000000000001</v>
       </c>
       <c r="X49">
-        <v>0.521</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="Y49">
-        <v>1.132</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>1.1319999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2019</v>
       </c>
       <c r="B50">
-        <v>37407.974</v>
+        <v>37407.974000000002</v>
       </c>
       <c r="C50">
-        <v>174.332</v>
+        <v>174.33199999999999</v>
       </c>
       <c r="E50">
         <v>0.187</v>
@@ -2975,19 +2922,19 @@
         <v>0.48</v>
       </c>
       <c r="G50">
-        <v>0.582</v>
+        <v>0.58199999999999996</v>
       </c>
       <c r="H50">
         <v>3784.27</v>
       </c>
       <c r="I50">
-        <v>174.664</v>
+        <v>174.66399999999999</v>
       </c>
       <c r="K50">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="L50">
-        <v>0.362</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="M50">
         <v>1.179</v>
@@ -3005,60 +2952,60 @@
         <v>0.253</v>
       </c>
       <c r="S50">
-        <v>0.9360000000000001</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="T50">
-        <v>31110.434</v>
+        <v>31110.434000000001</v>
       </c>
       <c r="U50">
         <v>180.65</v>
       </c>
       <c r="W50">
-        <v>0.177</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="X50">
-        <v>0.596</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="Y50">
-        <v>0.975</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>0.97499999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2020</v>
       </c>
       <c r="B51">
-        <v>33873.417</v>
+        <v>33873.417000000001</v>
       </c>
       <c r="C51">
-        <v>174.861</v>
+        <v>174.86099999999999</v>
       </c>
       <c r="E51">
         <v>0.185</v>
       </c>
       <c r="F51">
-        <v>0.488</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G51">
-        <v>0.603</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="H51">
         <v>3434.9</v>
       </c>
       <c r="I51">
-        <v>170.127</v>
+        <v>170.12700000000001</v>
       </c>
       <c r="K51">
-        <v>0.164</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="L51">
-        <v>0.319</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="M51">
-        <v>0.663</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="N51">
-        <v>2116.49</v>
+        <v>2116.4899999999998</v>
       </c>
       <c r="O51">
         <v>144.1</v>
@@ -3070,42 +3017,42 @@
         <v>0.224</v>
       </c>
       <c r="S51">
-        <v>0.822</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="T51">
-        <v>28322.027</v>
+        <v>28322.026999999998</v>
       </c>
       <c r="U51">
-        <v>186.692</v>
+        <v>186.69200000000001</v>
       </c>
       <c r="W51">
         <v>0.15</v>
       </c>
       <c r="X51">
-        <v>0.633</v>
+        <v>0.63300000000000001</v>
       </c>
       <c r="Y51">
-        <v>1.604</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>1.6040000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2021</v>
       </c>
       <c r="B52">
-        <v>33761.221</v>
+        <v>33761.220999999998</v>
       </c>
       <c r="C52">
-        <v>185.646</v>
+        <v>185.64599999999999</v>
       </c>
       <c r="E52">
         <v>0.15</v>
       </c>
       <c r="F52">
-        <v>0.553</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="G52">
-        <v>0.595</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="H52">
         <v>4629.16</v>
@@ -3117,7 +3064,7 @@
         <v>0.18</v>
       </c>
       <c r="L52">
-        <v>0.291</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="M52">
         <v>1.373</v>
@@ -3126,19 +3073,19 @@
         <v>1639.42</v>
       </c>
       <c r="S52">
-        <v>0.822</v>
+        <v>0.82199999999999995</v>
       </c>
       <c r="T52">
         <v>27492.641</v>
       </c>
       <c r="U52">
-        <v>190.324</v>
+        <v>190.32400000000001</v>
       </c>
       <c r="W52">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="X52">
-        <v>0.618</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="Y52">
         <v>0.89</v>

--- a/Indicator_4/Real_data/Blue_Shark_SAtl.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_SAtl.xlsx
@@ -1,300 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\EcoTest_Train\Indicator_4\Real_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{679DF415-758A-4353-9D0F-F5B50EF49D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Blue_Shark_SAtl</t>
-  </si>
-  <si>
-    <t>E.g. 'Swordfish_Natl'</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>max_age</t>
-  </si>
-  <si>
-    <t>14.184</t>
-  </si>
-  <si>
-    <t>Age to 5% natural survival</t>
-  </si>
-  <si>
-    <t>Life history</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>0.13</t>
-  </si>
-  <si>
-    <t>von Bertalannfy K</t>
-  </si>
-  <si>
-    <t>Linf</t>
-  </si>
-  <si>
-    <t>0.63</t>
-  </si>
-  <si>
-    <t>von Bertalannfy L-infinity (asymptotic length)</t>
-  </si>
-  <si>
-    <t>L50_Linf</t>
-  </si>
-  <si>
-    <t>291.8</t>
-  </si>
-  <si>
-    <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
-  </si>
-  <si>
-    <t>Total_L5_L50</t>
-  </si>
-  <si>
-    <t>0.423</t>
-  </si>
-  <si>
-    <t>Length at 5% selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Fleet selectivity</t>
-  </si>
-  <si>
-    <t>All fleets combined</t>
-  </si>
-  <si>
-    <t>Total_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.059</t>
-  </si>
-  <si>
-    <t>Length at full selection relative to length at 50% maturity</t>
-  </si>
-  <si>
-    <t>Total_VML</t>
-  </si>
-  <si>
-    <t>0.224</t>
-  </si>
-  <si>
-    <t>Selectivity of maximum length class</t>
-  </si>
-  <si>
-    <t>Fleet_1_L5_L50</t>
-  </si>
-  <si>
-    <t>0.615</t>
-  </si>
-  <si>
-    <t>Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet_1_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.021</t>
-  </si>
-  <si>
-    <t>Fleet_1_VML</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Fleet_2_L5_L50</t>
-  </si>
-  <si>
-    <t>0.445</t>
-  </si>
-  <si>
-    <t>Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_2_LFS_L50</t>
-  </si>
-  <si>
-    <t>0.998</t>
-  </si>
-  <si>
-    <t>Fleet_2_VML</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Fleet_3_L5_L50</t>
-  </si>
-  <si>
-    <t>0.408</t>
-  </si>
-  <si>
-    <t>Fleet 3</t>
-  </si>
-  <si>
-    <t>Fleet_3_LFS_L50</t>
-  </si>
-  <si>
-    <t>1.061</t>
-  </si>
-  <si>
-    <t>Fleet_3_VML</t>
-  </si>
-  <si>
-    <t>0.197</t>
-  </si>
-  <si>
-    <t>Fleet_1_CF</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 1</t>
-  </si>
-  <si>
-    <t>Fleet catch scale</t>
-  </si>
-  <si>
-    <t>Fleet_2_CF</t>
-  </si>
-  <si>
-    <t>0.212</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 2</t>
-  </si>
-  <si>
-    <t>Fleet_3_CF</t>
-  </si>
-  <si>
-    <t>0.719</t>
-  </si>
-  <si>
-    <t>Fraction of all historical catches that were Fleet 3</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Total_catch</t>
-  </si>
-  <si>
-    <t>Total_mean_len</t>
-  </si>
-  <si>
-    <t>Total_mean_age</t>
-  </si>
-  <si>
-    <t>Total_CV_len</t>
-  </si>
-  <si>
-    <t>Total_frac_mat</t>
-  </si>
-  <si>
-    <t>Total_Index</t>
-  </si>
-  <si>
-    <t>Fleet_1_catch</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_1_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_1_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_1_Index</t>
-  </si>
-  <si>
-    <t>Fleet_2_catch</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_2_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_2_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_2_Index</t>
-  </si>
-  <si>
-    <t>Fleet_3_catch</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_mean_age</t>
-  </si>
-  <si>
-    <t>Fleet_3_CV_len</t>
-  </si>
-  <si>
-    <t>Fleet_3_frac_mat</t>
-  </si>
-  <si>
-    <t>Fleet_3_Index</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,21 +64,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -394,7 +108,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -428,7 +142,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -463,10 +176,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -639,365 +351,575 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>61</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" t="s">
-        <v>57</v>
-      </c>
-      <c r="E21" t="s">
-        <v>49</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Blue_Shark_SAtl</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E.g. 'Swordfish_Natl'</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>max_age</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14.184</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Age to 5% natural survival</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>von Bertalannfy K</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Linf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>von Bertalannfy L-infinity (asymptotic length)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L50_Linf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>291.8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Length at 50% maturity relative to asymptotic length (von B. L-infinity)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life history</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Total_L5_L50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.423</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Total_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.059</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Total_VML</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>All fleets combined</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fleet_1_L5_L50</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fleet_1_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.021</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fleet_1_VML</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fleet_2_L5_L50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.445</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fleet_2_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.998</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fleet_2_VML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fleet_3_L5_L50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.408</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Length at 5% selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Fleet_3_LFS_L50</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.061</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Length at full selection relative to length at 50% maturity</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fleet_3_VML</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.197</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Selectivity of maximum length class</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fleet selectivity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fleet_1_CF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.069</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Fleet 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fleet_2_CF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.212</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fleet 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fleet_3_CF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.719</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fraction of all historical catches that were Fleet 3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Fleet catch scale</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Fleet 3</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1006,88 +928,138 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Y52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Total_catch</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_len</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Total_mean_age</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total_CV_len</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total_frac_mat</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Index</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_catch</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_len</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_mean_age</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_CV_len</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_frac_mat</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_1_Index</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_catch</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_len</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_mean_age</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_CV_len</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_frac_mat</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_2_Index</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_catch</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_len</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_mean_age</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_CV_len</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_frac_mat</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Fleet_3_Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1971</v>
       </c>
@@ -1095,130 +1067,130 @@
         <v>4732.317</v>
       </c>
       <c r="G2">
-        <v>1.6830000000000001</v>
+        <v>1.683</v>
       </c>
       <c r="H2">
-        <v>87.037000000000006</v>
+        <v>87.03700000000001</v>
       </c>
       <c r="N2">
-        <v>1132.3599999999999</v>
+        <v>1132.36</v>
       </c>
       <c r="T2">
         <v>3512.92</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3">
         <v>1972</v>
       </c>
       <c r="B3">
-        <v>5267.0990000000002</v>
+        <v>5267.099</v>
       </c>
       <c r="G3">
-        <v>1.4119999999999999</v>
+        <v>1.412</v>
       </c>
       <c r="H3">
-        <v>68.385999999999996</v>
+        <v>68.386</v>
       </c>
       <c r="N3">
-        <v>759.70299999999997</v>
+        <v>759.703</v>
       </c>
       <c r="T3">
         <v>4439.01</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4">
         <v>1973</v>
       </c>
       <c r="B4">
-        <v>6860.2830000000004</v>
+        <v>6860.283</v>
       </c>
       <c r="G4">
-        <v>1.4119999999999999</v>
+        <v>1.412</v>
       </c>
       <c r="H4">
-        <v>90.992999999999995</v>
+        <v>90.99299999999999</v>
       </c>
       <c r="N4">
         <v>2478.94</v>
       </c>
       <c r="T4">
-        <v>4290.3500000000004</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+        <v>4290.35</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>1974</v>
       </c>
       <c r="B5">
-        <v>4454.4030000000002</v>
+        <v>4454.403</v>
       </c>
       <c r="G5">
         <v>1.421</v>
       </c>
       <c r="H5">
-        <v>262.80500000000001</v>
+        <v>262.805</v>
       </c>
       <c r="N5">
-        <v>666.00800000000004</v>
+        <v>666.008</v>
       </c>
       <c r="T5">
         <v>3525.59</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6">
         <v>1975</v>
       </c>
       <c r="B6">
-        <v>4071.2640000000001</v>
+        <v>4071.264</v>
       </c>
       <c r="G6">
         <v>1.427</v>
       </c>
       <c r="H6">
-        <v>290.49900000000002</v>
+        <v>290.499</v>
       </c>
       <c r="N6">
-        <v>643.08500000000004</v>
+        <v>643.085</v>
       </c>
       <c r="T6">
         <v>3137.68</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7">
         <v>1976</v>
       </c>
       <c r="B7">
-        <v>4506.5060000000003</v>
+        <v>4506.506</v>
       </c>
       <c r="G7">
         <v>1.429</v>
       </c>
       <c r="H7">
-        <v>206.28800000000001</v>
+        <v>206.288</v>
       </c>
       <c r="N7">
-        <v>488.86799999999999</v>
+        <v>488.868</v>
       </c>
       <c r="T7">
         <v>3811.35</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8">
         <v>1977</v>
       </c>
       <c r="B8">
-        <v>9515.5059999999994</v>
+        <v>9515.505999999999</v>
       </c>
       <c r="G8">
-        <v>1.4379999999999999</v>
+        <v>1.438</v>
       </c>
       <c r="H8">
-        <v>217.02600000000001</v>
+        <v>217.026</v>
       </c>
       <c r="N8">
         <v>5764.68</v>
@@ -1227,7 +1199,7 @@
         <v>3533.8</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9">
         <v>1978</v>
       </c>
@@ -1235,10 +1207,10 @@
         <v>10503.758</v>
       </c>
       <c r="G9">
-        <v>1.4490000000000001</v>
+        <v>1.449</v>
       </c>
       <c r="H9">
-        <v>207.41800000000001</v>
+        <v>207.418</v>
       </c>
       <c r="N9">
         <v>6800.44</v>
@@ -1247,7 +1219,7 @@
         <v>3495.9</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10">
         <v>1979</v>
       </c>
@@ -1255,7 +1227,7 @@
         <v>11262.82</v>
       </c>
       <c r="G10">
-        <v>1.4590000000000001</v>
+        <v>1.459</v>
       </c>
       <c r="H10">
         <v>293.89</v>
@@ -1267,7 +1239,7 @@
         <v>3341.26</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11">
         <v>1980</v>
       </c>
@@ -1278,36 +1250,36 @@
         <v>1.452</v>
       </c>
       <c r="H11">
-        <v>892.40800000000002</v>
+        <v>892.408</v>
       </c>
       <c r="N11">
-        <v>8655.3799999999992</v>
+        <v>8655.379999999999</v>
       </c>
       <c r="T11">
         <v>3089.75</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12">
         <v>1981</v>
       </c>
       <c r="B12">
-        <v>7923.9849999999997</v>
+        <v>7923.985</v>
       </c>
       <c r="G12">
-        <v>1.4410000000000001</v>
+        <v>1.441</v>
       </c>
       <c r="H12">
-        <v>369.62299999999999</v>
+        <v>369.623</v>
       </c>
       <c r="N12">
         <v>4441.91</v>
       </c>
       <c r="T12">
-        <v>3112.4520000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+        <v>3112.452</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>1982</v>
       </c>
@@ -1327,12 +1299,12 @@
         <v>3420.895</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14">
         <v>1983</v>
       </c>
       <c r="B14">
-        <v>5949.6880000000001</v>
+        <v>5949.688</v>
       </c>
       <c r="G14">
         <v>1.409</v>
@@ -1344,21 +1316,21 @@
         <v>2813.28</v>
       </c>
       <c r="T14">
-        <v>2695.0079999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2695.008</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>1984</v>
       </c>
       <c r="B15">
-        <v>9958.8169999999991</v>
+        <v>9958.816999999999</v>
       </c>
       <c r="G15">
-        <v>1.4079999999999999</v>
+        <v>1.408</v>
       </c>
       <c r="H15">
-        <v>263.93599999999998</v>
+        <v>263.936</v>
       </c>
       <c r="N15">
         <v>7601.39</v>
@@ -1367,18 +1339,18 @@
         <v>2093.491</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16">
         <v>1985</v>
       </c>
       <c r="B16">
-        <v>8500.8359999999993</v>
+        <v>8500.835999999999</v>
       </c>
       <c r="G16">
         <v>1.389</v>
       </c>
       <c r="H16">
-        <v>317.62700000000001</v>
+        <v>317.627</v>
       </c>
       <c r="N16">
         <v>6155.67</v>
@@ -1387,7 +1359,7 @@
         <v>2027.539</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17">
         <v>1986</v>
       </c>
@@ -1395,7 +1367,7 @@
         <v>12003.017</v>
       </c>
       <c r="G17">
-        <v>1.3959999999999999</v>
+        <v>1.396</v>
       </c>
       <c r="H17">
         <v>425.01</v>
@@ -1404,81 +1376,81 @@
         <v>7716.97</v>
       </c>
       <c r="T17">
-        <v>3861.0369999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>3861.037</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>1987</v>
       </c>
       <c r="B18">
-        <v>9586.5869999999995</v>
+        <v>9586.587</v>
       </c>
       <c r="G18">
         <v>1.391</v>
       </c>
       <c r="H18">
-        <v>535.21900000000005</v>
+        <v>535.2190000000001</v>
       </c>
       <c r="N18">
         <v>4706.75</v>
       </c>
       <c r="T18">
-        <v>4344.6180000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+        <v>4344.618</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>1988</v>
       </c>
       <c r="B19">
-        <v>16927.941999999999</v>
+        <v>16927.942</v>
       </c>
       <c r="G19">
         <v>1.391</v>
       </c>
       <c r="H19">
-        <v>656.73099999999999</v>
+        <v>656.731</v>
       </c>
       <c r="N19">
         <v>7016.24</v>
       </c>
       <c r="T19">
-        <v>9254.9709999999995</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+        <v>9254.971</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>1989</v>
       </c>
       <c r="B20">
-        <v>21996.896000000001</v>
+        <v>21996.896</v>
       </c>
       <c r="G20">
         <v>1.379</v>
       </c>
       <c r="H20">
-        <v>660.12199999999996</v>
+        <v>660.122</v>
       </c>
       <c r="N20">
         <v>6806.85</v>
       </c>
       <c r="T20">
-        <v>14529.924000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+        <v>14529.924</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>1990</v>
       </c>
       <c r="B21">
-        <v>25184.942999999999</v>
+        <v>25184.943</v>
       </c>
       <c r="G21">
         <v>1.375</v>
       </c>
       <c r="H21">
-        <v>958.53300000000002</v>
+        <v>958.533</v>
       </c>
       <c r="N21">
         <v>8058.33</v>
@@ -1487,18 +1459,18 @@
         <v>16168.08</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22">
         <v>1991</v>
       </c>
       <c r="B22">
-        <v>21219.331999999999</v>
+        <v>21219.332</v>
       </c>
       <c r="G22">
         <v>1.345</v>
       </c>
       <c r="H22">
-        <v>741.50699999999995</v>
+        <v>741.5069999999999</v>
       </c>
       <c r="N22">
         <v>6559.97</v>
@@ -1507,30 +1479,30 @@
         <v>13917.855</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23">
         <v>1992</v>
       </c>
       <c r="B23">
-        <v>23229.132000000001</v>
+        <v>23229.132</v>
       </c>
       <c r="G23">
-        <v>1.2949999999999999</v>
+        <v>1.295</v>
       </c>
       <c r="H23">
         <v>1474.54</v>
       </c>
       <c r="N23">
-        <v>4748.2299999999996</v>
+        <v>4748.23</v>
       </c>
       <c r="T23">
-        <v>17006.362000000001</v>
+        <v>17006.362</v>
       </c>
       <c r="Y23">
-        <v>1.4139999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.414</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>1993</v>
       </c>
@@ -1538,16 +1510,16 @@
         <v>23127.734</v>
       </c>
       <c r="C24">
-        <v>201.46899999999999</v>
+        <v>201.469</v>
       </c>
       <c r="E24">
         <v>0.16</v>
       </c>
       <c r="F24">
-        <v>0.80900000000000005</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="G24">
-        <v>1.2390000000000001</v>
+        <v>1.239</v>
       </c>
       <c r="H24">
         <v>1137.69</v>
@@ -1556,63 +1528,63 @@
         <v>7833.96</v>
       </c>
       <c r="T24">
-        <v>14156.084000000001</v>
+        <v>14156.084</v>
       </c>
       <c r="U24">
-        <v>201.46899999999999</v>
+        <v>201.469</v>
       </c>
       <c r="W24">
         <v>0.16</v>
       </c>
       <c r="X24">
-        <v>0.80900000000000005</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Y24">
-        <v>0.93799999999999994</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.9379999999999999</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>1994</v>
       </c>
       <c r="B25">
-        <v>26721.239000000001</v>
+        <v>26721.239</v>
       </c>
       <c r="C25">
-        <v>199.87700000000001</v>
+        <v>199.877</v>
       </c>
       <c r="E25">
         <v>0.13</v>
       </c>
       <c r="F25">
-        <v>0.78900000000000003</v>
+        <v>0.789</v>
       </c>
       <c r="G25">
         <v>1.2</v>
       </c>
       <c r="H25">
-        <v>887.88699999999994</v>
+        <v>887.8869999999999</v>
       </c>
       <c r="N25">
         <v>7658.81</v>
       </c>
       <c r="T25">
-        <v>18174.542000000001</v>
+        <v>18174.542</v>
       </c>
       <c r="U25">
-        <v>199.87700000000001</v>
+        <v>199.877</v>
       </c>
       <c r="W25">
         <v>0.13</v>
       </c>
       <c r="X25">
-        <v>0.78900000000000003</v>
+        <v>0.789</v>
       </c>
       <c r="Y25">
-        <v>0.90400000000000003</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.904</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>1995</v>
       </c>
@@ -1623,101 +1595,101 @@
         <v>199.428</v>
       </c>
       <c r="E26">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="F26">
-        <v>0.76400000000000001</v>
+        <v>0.764</v>
       </c>
       <c r="G26">
-        <v>1.1599999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="H26">
-        <v>1113.3900000000001</v>
+        <v>1113.39</v>
       </c>
       <c r="N26">
         <v>5555.57</v>
       </c>
       <c r="T26">
-        <v>22140.452000000001</v>
+        <v>22140.452</v>
       </c>
       <c r="U26">
         <v>199.428</v>
       </c>
       <c r="W26">
-        <v>0.13400000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="X26">
-        <v>0.76400000000000001</v>
+        <v>0.764</v>
       </c>
       <c r="Y26">
-        <v>0.83799999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.838</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>1996</v>
       </c>
       <c r="B27">
-        <v>30158.112000000001</v>
+        <v>30158.112</v>
       </c>
       <c r="C27">
-        <v>157.61099999999999</v>
+        <v>157.611</v>
       </c>
       <c r="E27">
-        <v>0.19600000000000001</v>
+        <v>0.196</v>
       </c>
       <c r="F27">
-        <v>0.35699999999999998</v>
+        <v>0.357</v>
       </c>
       <c r="G27">
-        <v>1.1240000000000001</v>
+        <v>1.124</v>
       </c>
       <c r="H27">
         <v>1069.31</v>
       </c>
       <c r="N27">
-        <v>4851.8100000000004</v>
+        <v>4851.81</v>
       </c>
       <c r="O27">
-        <v>119.11799999999999</v>
+        <v>119.118</v>
       </c>
       <c r="Q27">
-        <v>0.27500000000000002</v>
+        <v>0.275</v>
       </c>
       <c r="R27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>24236.991999999998</v>
+        <v>24236.992</v>
       </c>
       <c r="U27">
-        <v>196.10499999999999</v>
+        <v>196.105</v>
       </c>
       <c r="W27">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="X27">
-        <v>0.71299999999999997</v>
+        <v>0.713</v>
       </c>
       <c r="Y27">
-        <v>0.73599999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.736</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>1997</v>
       </c>
       <c r="B28">
-        <v>23105.817999999999</v>
+        <v>23105.818</v>
       </c>
       <c r="C28">
-        <v>200.97200000000001</v>
+        <v>200.972</v>
       </c>
       <c r="E28">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="F28">
-        <v>0.81100000000000005</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="G28">
         <v>1.056</v>
@@ -1726,16 +1698,16 @@
         <v>2317.21</v>
       </c>
       <c r="N28">
-        <v>4396.5200000000004</v>
+        <v>4396.52</v>
       </c>
       <c r="O28">
-        <v>202.47499999999999</v>
+        <v>202.475</v>
       </c>
       <c r="Q28">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="R28">
-        <v>0.82799999999999996</v>
+        <v>0.828</v>
       </c>
       <c r="T28">
         <v>16392.088</v>
@@ -1747,13 +1719,13 @@
         <v>0.104</v>
       </c>
       <c r="X28">
-        <v>0.79400000000000004</v>
+        <v>0.794</v>
       </c>
       <c r="Y28">
-        <v>0.77500000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.775</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>1998</v>
       </c>
@@ -1761,45 +1733,45 @@
         <v>21501.678</v>
       </c>
       <c r="C29">
-        <v>203.53100000000001</v>
+        <v>203.531</v>
       </c>
       <c r="E29">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="F29">
-        <v>0.77500000000000002</v>
+        <v>0.775</v>
       </c>
       <c r="G29">
-        <v>0.95399999999999996</v>
+        <v>0.954</v>
       </c>
       <c r="H29">
-        <v>2172.5300000000002</v>
+        <v>2172.53</v>
       </c>
       <c r="N29">
         <v>3720.34</v>
       </c>
       <c r="T29">
-        <v>15608.808000000001</v>
+        <v>15608.808</v>
       </c>
       <c r="U29">
-        <v>203.53100000000001</v>
+        <v>203.531</v>
       </c>
       <c r="W29">
-        <v>0.13500000000000001</v>
+        <v>0.135</v>
       </c>
       <c r="X29">
-        <v>0.77500000000000002</v>
+        <v>0.775</v>
       </c>
       <c r="Y29">
         <v>0.84</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30">
         <v>1999</v>
       </c>
       <c r="B30">
-        <v>23001.219000000001</v>
+        <v>23001.219</v>
       </c>
       <c r="C30">
         <v>185.94</v>
@@ -1808,10 +1780,10 @@
         <v>0.222</v>
       </c>
       <c r="F30">
-        <v>0.63900000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="G30">
-        <v>0.83799999999999997</v>
+        <v>0.838</v>
       </c>
       <c r="H30">
         <v>2668.18</v>
@@ -1820,16 +1792,16 @@
         <v>3133.5</v>
       </c>
       <c r="O30">
-        <v>142.97499999999999</v>
+        <v>142.975</v>
       </c>
       <c r="Q30">
-        <v>0.35299999999999998</v>
+        <v>0.353</v>
       </c>
       <c r="R30">
         <v>0.24</v>
       </c>
       <c r="T30">
-        <v>17199.539000000001</v>
+        <v>17199.539</v>
       </c>
       <c r="U30">
         <v>207.422</v>
@@ -1838,30 +1810,30 @@
         <v>0.156</v>
       </c>
       <c r="X30">
-        <v>0.83799999999999997</v>
+        <v>0.838</v>
       </c>
       <c r="Y30">
-        <v>0.80200000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.802</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>2000</v>
       </c>
       <c r="B31">
-        <v>23089.132000000001</v>
+        <v>23089.132</v>
       </c>
       <c r="C31">
-        <v>160.41800000000001</v>
+        <v>160.418</v>
       </c>
       <c r="E31">
-        <v>0.22800000000000001</v>
+        <v>0.228</v>
       </c>
       <c r="F31">
-        <v>0.35499999999999998</v>
+        <v>0.355</v>
       </c>
       <c r="G31">
-        <v>0.75900000000000001</v>
+        <v>0.759</v>
       </c>
       <c r="H31">
         <v>1682.5</v>
@@ -1870,48 +1842,48 @@
         <v>2950.82</v>
       </c>
       <c r="O31">
-        <v>132.59800000000001</v>
+        <v>132.598</v>
       </c>
       <c r="Q31">
-        <v>0.26800000000000002</v>
+        <v>0.268</v>
       </c>
       <c r="R31">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="T31">
-        <v>18455.812000000002</v>
+        <v>18455.812</v>
       </c>
       <c r="U31">
-        <v>174.32900000000001</v>
+        <v>174.329</v>
       </c>
       <c r="W31">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="X31">
-        <v>0.51300000000000001</v>
+        <v>0.513</v>
       </c>
       <c r="Y31">
-        <v>0.82799999999999996</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.828</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>2001</v>
       </c>
       <c r="B32">
-        <v>20808.508000000002</v>
+        <v>20808.508</v>
       </c>
       <c r="C32">
-        <v>176.60499999999999</v>
+        <v>176.605</v>
       </c>
       <c r="E32">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="F32">
         <v>0.52</v>
       </c>
       <c r="G32">
-        <v>0.70499999999999996</v>
+        <v>0.705</v>
       </c>
       <c r="H32">
         <v>2173.4</v>
@@ -1920,16 +1892,16 @@
         <v>1666.67</v>
       </c>
       <c r="O32">
-        <v>166.01400000000001</v>
+        <v>166.014</v>
       </c>
       <c r="Q32">
         <v>0.311</v>
       </c>
       <c r="R32">
-        <v>0.41899999999999998</v>
+        <v>0.419</v>
       </c>
       <c r="T32">
-        <v>16968.437999999998</v>
+        <v>16968.438</v>
       </c>
       <c r="U32">
         <v>181.9</v>
@@ -1938,30 +1910,30 @@
         <v>0.154</v>
       </c>
       <c r="X32">
-        <v>0.57099999999999995</v>
+        <v>0.571</v>
       </c>
       <c r="Y32">
-        <v>0.80400000000000005</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.804</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>2002</v>
       </c>
       <c r="B33">
-        <v>22166.300999999999</v>
+        <v>22166.301</v>
       </c>
       <c r="C33">
         <v>173.483</v>
       </c>
       <c r="E33">
-        <v>0.20899999999999999</v>
+        <v>0.209</v>
       </c>
       <c r="F33">
-        <v>0.40300000000000002</v>
+        <v>0.403</v>
       </c>
       <c r="G33">
-        <v>0.65800000000000003</v>
+        <v>0.658</v>
       </c>
       <c r="H33">
         <v>1970.5</v>
@@ -1970,16 +1942,16 @@
         <v>1446.59</v>
       </c>
       <c r="O33">
-        <v>172.80699999999999</v>
+        <v>172.807</v>
       </c>
       <c r="Q33">
-        <v>0.20599999999999999</v>
+        <v>0.206</v>
       </c>
       <c r="R33">
-        <v>0.39900000000000002</v>
+        <v>0.399</v>
       </c>
       <c r="T33">
-        <v>18749.210999999999</v>
+        <v>18749.211</v>
       </c>
       <c r="U33">
         <v>173.82</v>
@@ -1988,39 +1960,39 @@
         <v>0.21</v>
       </c>
       <c r="X33">
-        <v>0.40600000000000003</v>
+        <v>0.406</v>
       </c>
       <c r="Y33">
-        <v>0.77900000000000003</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.779</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34">
         <v>2003</v>
       </c>
       <c r="B34">
-        <v>26719.467000000001</v>
+        <v>26719.467</v>
       </c>
       <c r="C34">
-        <v>171.05099999999999</v>
+        <v>171.051</v>
       </c>
       <c r="E34">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="F34">
         <v>0.378</v>
       </c>
       <c r="G34">
-        <v>0.61099999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="H34">
-        <v>2165.7600000000002</v>
+        <v>2165.76</v>
       </c>
       <c r="N34">
         <v>5469.22</v>
       </c>
       <c r="O34">
-        <v>176.70099999999999</v>
+        <v>176.701</v>
       </c>
       <c r="Q34">
         <v>0.223</v>
@@ -2029,39 +2001,39 @@
         <v>0.442</v>
       </c>
       <c r="T34">
-        <v>19084.487000000001</v>
+        <v>19084.487</v>
       </c>
       <c r="U34">
-        <v>168.22499999999999</v>
+        <v>168.225</v>
       </c>
       <c r="W34">
-        <v>0.20699999999999999</v>
+        <v>0.207</v>
       </c>
       <c r="X34">
-        <v>0.34599999999999997</v>
+        <v>0.346</v>
       </c>
       <c r="Y34">
-        <v>0.82499999999999996</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.825</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>2004</v>
       </c>
       <c r="B35">
-        <v>22402.670999999998</v>
+        <v>22402.671</v>
       </c>
       <c r="C35">
-        <v>165.25399999999999</v>
+        <v>165.254</v>
       </c>
       <c r="E35">
         <v>0.246</v>
       </c>
       <c r="F35">
-        <v>0.34499999999999997</v>
+        <v>0.345</v>
       </c>
       <c r="G35">
-        <v>0.57499999999999996</v>
+        <v>0.575</v>
       </c>
       <c r="H35">
         <v>1667.36</v>
@@ -2070,39 +2042,39 @@
         <v>2680.3</v>
       </c>
       <c r="T35">
-        <v>18055.010999999999</v>
+        <v>18055.011</v>
       </c>
       <c r="U35">
-        <v>165.25399999999999</v>
+        <v>165.254</v>
       </c>
       <c r="W35">
         <v>0.246</v>
       </c>
       <c r="X35">
-        <v>0.34499999999999997</v>
+        <v>0.345</v>
       </c>
       <c r="Y35">
-        <v>0.76600000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.766</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>2005</v>
       </c>
       <c r="B36">
-        <v>26593.075000000001</v>
+        <v>26593.075</v>
       </c>
       <c r="C36">
-        <v>180.09399999999999</v>
+        <v>180.094</v>
       </c>
       <c r="E36">
-        <v>0.21299999999999999</v>
+        <v>0.213</v>
       </c>
       <c r="F36">
         <v>0.49</v>
       </c>
       <c r="G36">
-        <v>0.55700000000000005</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H36">
         <v>2523.27</v>
@@ -2123,28 +2095,28 @@
         <v>146.846</v>
       </c>
       <c r="Q36">
-        <v>0.25700000000000001</v>
+        <v>0.257</v>
       </c>
       <c r="R36">
-        <v>0.13800000000000001</v>
+        <v>0.138</v>
       </c>
       <c r="T36">
-        <v>22409.575000000001</v>
+        <v>22409.575</v>
       </c>
       <c r="U36">
         <v>189.77</v>
       </c>
       <c r="W36">
-        <v>0.20300000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="X36">
-        <v>0.59399999999999997</v>
+        <v>0.594</v>
       </c>
       <c r="Y36">
-        <v>0.84199999999999997</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.842</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>2006</v>
       </c>
@@ -2152,40 +2124,40 @@
         <v>24446.04</v>
       </c>
       <c r="C37">
-        <v>184.72300000000001</v>
+        <v>184.723</v>
       </c>
       <c r="E37">
         <v>0.185</v>
       </c>
       <c r="F37">
-        <v>0.54800000000000004</v>
+        <v>0.548</v>
       </c>
       <c r="G37">
-        <v>0.54300000000000004</v>
+        <v>0.543</v>
       </c>
       <c r="H37">
         <v>2591.33</v>
       </c>
       <c r="I37">
-        <v>185.78200000000001</v>
+        <v>185.782</v>
       </c>
       <c r="K37">
         <v>0.189</v>
       </c>
       <c r="L37">
-        <v>0.45800000000000002</v>
+        <v>0.458</v>
       </c>
       <c r="N37">
         <v>3281.84</v>
       </c>
       <c r="O37">
-        <v>167.57599999999999</v>
+        <v>167.576</v>
       </c>
       <c r="Q37">
-        <v>0.23200000000000001</v>
+        <v>0.232</v>
       </c>
       <c r="R37">
-        <v>0.42399999999999999</v>
+        <v>0.424</v>
       </c>
       <c r="T37">
         <v>18572.87</v>
@@ -2194,16 +2166,16 @@
         <v>187.941</v>
       </c>
       <c r="W37">
-        <v>0.17499999999999999</v>
+        <v>0.175</v>
       </c>
       <c r="X37">
-        <v>0.59099999999999997</v>
+        <v>0.591</v>
       </c>
       <c r="Y37">
-        <v>0.88600000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.886</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38">
         <v>2007</v>
       </c>
@@ -2211,16 +2183,16 @@
         <v>26571.555</v>
       </c>
       <c r="C38">
-        <v>165.68899999999999</v>
+        <v>165.689</v>
       </c>
       <c r="E38">
-        <v>0.22700000000000001</v>
+        <v>0.227</v>
       </c>
       <c r="F38">
-        <v>0.29099999999999998</v>
+        <v>0.291</v>
       </c>
       <c r="G38">
-        <v>0.54200000000000004</v>
+        <v>0.542</v>
       </c>
       <c r="H38">
         <v>2645.28</v>
@@ -2229,31 +2201,31 @@
         <v>153.267</v>
       </c>
       <c r="K38">
-        <v>0.22500000000000001</v>
+        <v>0.225</v>
       </c>
       <c r="L38">
-        <v>0.19500000000000001</v>
+        <v>0.195</v>
       </c>
       <c r="N38">
         <v>3653.3</v>
       </c>
       <c r="T38">
-        <v>20272.974999999999</v>
+        <v>20272.975</v>
       </c>
       <c r="U38">
-        <v>168.79400000000001</v>
+        <v>168.794</v>
       </c>
       <c r="W38">
-        <v>0.22800000000000001</v>
+        <v>0.228</v>
       </c>
       <c r="X38">
         <v>0.315</v>
       </c>
       <c r="Y38">
-        <v>0.90900000000000003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.909</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>2008</v>
       </c>
@@ -2261,31 +2233,31 @@
         <v>26841.428</v>
       </c>
       <c r="C39">
-        <v>190.37700000000001</v>
+        <v>190.377</v>
       </c>
       <c r="E39">
-        <v>0.17899999999999999</v>
+        <v>0.179</v>
       </c>
       <c r="F39">
-        <v>0.61099999999999999</v>
+        <v>0.611</v>
       </c>
       <c r="G39">
-        <v>0.51800000000000002</v>
+        <v>0.518</v>
       </c>
       <c r="H39">
         <v>2012.58</v>
       </c>
       <c r="I39">
-        <v>214.88499999999999</v>
+        <v>214.885</v>
       </c>
       <c r="K39">
-        <v>0.16500000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="L39">
-        <v>0.85799999999999998</v>
+        <v>0.858</v>
       </c>
       <c r="M39">
-        <v>0.79300000000000004</v>
+        <v>0.793</v>
       </c>
       <c r="N39">
         <v>5521.34</v>
@@ -2294,16 +2266,16 @@
         <v>188.6</v>
       </c>
       <c r="Q39">
-        <v>0.16700000000000001</v>
+        <v>0.167</v>
       </c>
       <c r="R39">
-        <v>0.57999999999999996</v>
+        <v>0.58</v>
       </c>
       <c r="S39">
-        <v>1.0189999999999999</v>
+        <v>1.019</v>
       </c>
       <c r="T39">
-        <v>19307.508000000002</v>
+        <v>19307.508</v>
       </c>
       <c r="U39">
         <v>185.83</v>
@@ -2312,13 +2284,13 @@
         <v>0.184</v>
       </c>
       <c r="X39">
-        <v>0.56799999999999995</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="Y39">
-        <v>1.0089999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.009</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>2009</v>
       </c>
@@ -2326,10 +2298,10 @@
         <v>26421.572</v>
       </c>
       <c r="C40">
-        <v>180.85400000000001</v>
+        <v>180.854</v>
       </c>
       <c r="E40">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="F40">
         <v>0.502</v>
@@ -2341,19 +2313,19 @@
         <v>1273.5</v>
       </c>
       <c r="M40">
-        <v>0.83799999999999997</v>
+        <v>0.838</v>
       </c>
       <c r="N40">
         <v>3768</v>
       </c>
       <c r="O40">
-        <v>170.52199999999999</v>
+        <v>170.522</v>
       </c>
       <c r="Q40">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="R40">
-        <v>0.29899999999999999</v>
+        <v>0.299</v>
       </c>
       <c r="S40">
         <v>0.92</v>
@@ -2362,72 +2334,72 @@
         <v>21380.072</v>
       </c>
       <c r="U40">
-        <v>183.43700000000001</v>
+        <v>183.437</v>
       </c>
       <c r="W40">
-        <v>0.16200000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="X40">
-        <v>0.55300000000000005</v>
+        <v>0.553</v>
       </c>
       <c r="Y40">
         <v>0.96</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41">
         <v>2010</v>
       </c>
       <c r="B41">
-        <v>31973.757000000001</v>
+        <v>31973.757</v>
       </c>
       <c r="C41">
-        <v>175.57300000000001</v>
+        <v>175.573</v>
       </c>
       <c r="E41">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="F41">
-        <v>0.40300000000000002</v>
+        <v>0.403</v>
       </c>
       <c r="G41">
-        <v>0.48899999999999999</v>
+        <v>0.489</v>
       </c>
       <c r="H41">
         <v>1500.5</v>
       </c>
       <c r="I41">
-        <v>205.52799999999999</v>
+        <v>205.528</v>
       </c>
       <c r="K41">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="L41">
-        <v>0.68799999999999994</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="M41">
-        <v>0.75600000000000001</v>
+        <v>0.756</v>
       </c>
       <c r="N41">
         <v>5335.59</v>
       </c>
       <c r="O41">
-        <v>158.72900000000001</v>
+        <v>158.729</v>
       </c>
       <c r="Q41">
         <v>0.11</v>
       </c>
       <c r="R41">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="S41">
         <v>1.264</v>
       </c>
       <c r="T41">
-        <v>25137.667000000001</v>
+        <v>25137.667</v>
       </c>
       <c r="U41">
-        <v>172.95099999999999</v>
+        <v>172.951</v>
       </c>
       <c r="W41">
         <v>0.185</v>
@@ -2436,24 +2408,24 @@
         <v>0.42</v>
       </c>
       <c r="Y41">
-        <v>1.1619999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.162</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>2011</v>
       </c>
       <c r="B42">
-        <v>37684.955999999998</v>
+        <v>37684.956</v>
       </c>
       <c r="C42">
-        <v>177.63900000000001</v>
+        <v>177.639</v>
       </c>
       <c r="E42">
-        <v>0.17799999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="F42">
-        <v>0.48799999999999999</v>
+        <v>0.488</v>
       </c>
       <c r="G42">
         <v>0.48</v>
@@ -2474,33 +2446,33 @@
         <v>0.128</v>
       </c>
       <c r="R42">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="S42">
         <v>1.294</v>
       </c>
       <c r="T42">
-        <v>31463.256000000001</v>
+        <v>31463.256</v>
       </c>
       <c r="U42">
-        <v>180.49199999999999</v>
+        <v>180.492</v>
       </c>
       <c r="W42">
         <v>0.187</v>
       </c>
       <c r="X42">
-        <v>0.55300000000000005</v>
+        <v>0.553</v>
       </c>
       <c r="Y42">
-        <v>0.92100000000000004</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.921</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>2012</v>
       </c>
       <c r="B43">
-        <v>27734.505000000001</v>
+        <v>27734.505</v>
       </c>
       <c r="C43">
         <v>173.8</v>
@@ -2509,49 +2481,49 @@
         <v>0.161</v>
       </c>
       <c r="F43">
-        <v>0.39600000000000002</v>
+        <v>0.396</v>
       </c>
       <c r="G43">
-        <v>0.47699999999999998</v>
+        <v>0.477</v>
       </c>
       <c r="H43">
         <v>1607.26</v>
       </c>
       <c r="M43">
-        <v>1.4550000000000001</v>
+        <v>1.455</v>
       </c>
       <c r="N43">
-        <v>4447.3599999999997</v>
+        <v>4447.36</v>
       </c>
       <c r="O43">
-        <v>168.94200000000001</v>
+        <v>168.942</v>
       </c>
       <c r="Q43">
-        <v>0.23499999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="R43">
-        <v>0.32700000000000001</v>
+        <v>0.327</v>
       </c>
       <c r="S43">
         <v>1.004</v>
       </c>
       <c r="T43">
-        <v>21679.884999999998</v>
+        <v>21679.885</v>
       </c>
       <c r="U43">
-        <v>174.77099999999999</v>
+        <v>174.771</v>
       </c>
       <c r="W43">
-        <v>0.14699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="X43">
         <v>0.41</v>
       </c>
       <c r="Y43">
-        <v>1.1910000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.191</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>2013</v>
       </c>
@@ -2559,16 +2531,16 @@
         <v>20799.125</v>
       </c>
       <c r="C44">
-        <v>175.57400000000001</v>
+        <v>175.574</v>
       </c>
       <c r="E44">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="F44">
         <v>0.43</v>
       </c>
       <c r="G44">
-        <v>0.46899999999999997</v>
+        <v>0.469</v>
       </c>
       <c r="H44">
         <v>1008.13</v>
@@ -2580,57 +2552,57 @@
         <v>3509.4</v>
       </c>
       <c r="O44">
-        <v>169.44800000000001</v>
+        <v>169.448</v>
       </c>
       <c r="Q44">
-        <v>0.21199999999999999</v>
+        <v>0.212</v>
       </c>
       <c r="R44">
-        <v>0.35499999999999998</v>
+        <v>0.355</v>
       </c>
       <c r="S44">
         <v>1.081</v>
       </c>
       <c r="T44">
-        <v>16281.594999999999</v>
+        <v>16281.595</v>
       </c>
       <c r="U44">
-        <v>176.79900000000001</v>
+        <v>176.799</v>
       </c>
       <c r="W44">
         <v>0.154</v>
       </c>
       <c r="X44">
-        <v>0.44500000000000001</v>
+        <v>0.445</v>
       </c>
       <c r="Y44">
         <v>1.214</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45">
         <v>2014</v>
       </c>
       <c r="B45">
-        <v>26252.799999999999</v>
+        <v>26252.8</v>
       </c>
       <c r="C45">
-        <v>178.34899999999999</v>
+        <v>178.349</v>
       </c>
       <c r="E45">
         <v>0.156</v>
       </c>
       <c r="F45">
-        <v>0.45500000000000002</v>
+        <v>0.455</v>
       </c>
       <c r="G45">
-        <v>0.44400000000000001</v>
+        <v>0.444</v>
       </c>
       <c r="H45">
         <v>2551.41</v>
       </c>
       <c r="M45">
-        <v>0.85699999999999998</v>
+        <v>0.857</v>
       </c>
       <c r="N45">
         <v>3232</v>
@@ -2642,7 +2614,7 @@
         <v>0.185</v>
       </c>
       <c r="R45">
-        <v>0.54800000000000004</v>
+        <v>0.548</v>
       </c>
       <c r="S45">
         <v>1.157</v>
@@ -2654,7 +2626,7 @@
         <v>176.928</v>
       </c>
       <c r="W45">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="X45">
         <v>0.432</v>
@@ -2663,7 +2635,7 @@
         <v>1.357</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46">
         <v>2015</v>
       </c>
@@ -2671,34 +2643,34 @@
         <v>22498.5</v>
       </c>
       <c r="C46">
-        <v>177.35300000000001</v>
+        <v>177.353</v>
       </c>
       <c r="E46">
-        <v>0.13600000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="F46">
-        <v>0.50800000000000001</v>
+        <v>0.508</v>
       </c>
       <c r="G46">
-        <v>0.46700000000000003</v>
+        <v>0.467</v>
       </c>
       <c r="H46">
-        <v>2420.4699999999998</v>
+        <v>2420.47</v>
       </c>
       <c r="M46">
-        <v>1.0960000000000001</v>
+        <v>1.096</v>
       </c>
       <c r="N46">
         <v>2277.42</v>
       </c>
       <c r="O46">
-        <v>159.21199999999999</v>
+        <v>159.212</v>
       </c>
       <c r="Q46">
-        <v>0.20200000000000001</v>
+        <v>0.202</v>
       </c>
       <c r="R46">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="S46">
         <v>0.89</v>
@@ -2707,7 +2679,7 @@
         <v>17800.61</v>
       </c>
       <c r="U46">
-        <v>181.88900000000001</v>
+        <v>181.889</v>
       </c>
       <c r="W46">
         <v>0.12</v>
@@ -2719,7 +2691,7 @@
         <v>1.111</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47">
         <v>2016</v>
       </c>
@@ -2736,28 +2708,28 @@
         <v>0.374</v>
       </c>
       <c r="G47">
-        <v>0.51800000000000002</v>
+        <v>0.518</v>
       </c>
       <c r="H47">
         <v>1334.3</v>
       </c>
       <c r="M47">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N47">
-        <v>2127.3000000000002</v>
+        <v>2127.3</v>
       </c>
       <c r="O47">
-        <v>155.51599999999999</v>
+        <v>155.516</v>
       </c>
       <c r="Q47">
-        <v>0.23499999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="R47">
         <v>0.192</v>
       </c>
       <c r="S47">
-        <v>0.92800000000000005</v>
+        <v>0.928</v>
       </c>
       <c r="T47">
         <v>21955.08</v>
@@ -2766,16 +2738,16 @@
         <v>174.209</v>
       </c>
       <c r="W47">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="X47">
-        <v>0.41899999999999998</v>
+        <v>0.419</v>
       </c>
       <c r="Y47">
         <v>1.486</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48">
         <v>2017</v>
       </c>
@@ -2789,25 +2761,25 @@
         <v>0.182</v>
       </c>
       <c r="F48">
-        <v>0.45400000000000001</v>
+        <v>0.454</v>
       </c>
       <c r="G48">
-        <v>0.54500000000000004</v>
+        <v>0.545</v>
       </c>
       <c r="H48">
-        <v>2176.7199999999998</v>
+        <v>2176.72</v>
       </c>
       <c r="I48">
-        <v>181.02600000000001</v>
+        <v>181.026</v>
       </c>
       <c r="K48">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="L48">
         <v>0.41</v>
       </c>
       <c r="M48">
-        <v>0.93899999999999995</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="N48">
         <v>3111.65</v>
@@ -2816,13 +2788,13 @@
         <v>167.25</v>
       </c>
       <c r="Q48">
-        <v>0.28299999999999997</v>
+        <v>0.283</v>
       </c>
       <c r="R48">
-        <v>0.47099999999999997</v>
+        <v>0.471</v>
       </c>
       <c r="S48">
-        <v>0.92800000000000005</v>
+        <v>0.928</v>
       </c>
       <c r="T48">
         <v>23266.52</v>
@@ -2831,39 +2803,39 @@
         <v>174.476</v>
       </c>
       <c r="W48">
-        <v>0.17100000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="X48">
-        <v>0.45900000000000002</v>
+        <v>0.459</v>
       </c>
       <c r="Y48">
-        <v>1.1020000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.102</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>2018</v>
       </c>
       <c r="B49">
-        <v>34513.980000000003</v>
+        <v>34513.98</v>
       </c>
       <c r="C49">
-        <v>177.36500000000001</v>
+        <v>177.365</v>
       </c>
       <c r="E49">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="F49">
-        <v>0.51400000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="G49">
-        <v>0.56599999999999995</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H49">
         <v>3010.73</v>
       </c>
       <c r="I49">
-        <v>177.62700000000001</v>
+        <v>177.627</v>
       </c>
       <c r="K49">
         <v>0.125</v>
@@ -2872,48 +2844,48 @@
         <v>0.374</v>
       </c>
       <c r="M49">
-        <v>1.1419999999999999</v>
+        <v>1.142</v>
       </c>
       <c r="N49">
         <v>3495.36</v>
       </c>
       <c r="O49">
-        <v>182.63499999999999</v>
+        <v>182.635</v>
       </c>
       <c r="Q49">
-        <v>0.20799999999999999</v>
+        <v>0.208</v>
       </c>
       <c r="R49">
-        <v>0.61399999999999999</v>
+        <v>0.614</v>
       </c>
       <c r="S49">
-        <v>0.93600000000000005</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="T49">
         <v>28007.89</v>
       </c>
       <c r="U49">
-        <v>176.44300000000001</v>
+        <v>176.443</v>
       </c>
       <c r="W49">
-        <v>0.16600000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="X49">
-        <v>0.52100000000000002</v>
+        <v>0.521</v>
       </c>
       <c r="Y49">
-        <v>1.1319999999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.132</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>2019</v>
       </c>
       <c r="B50">
-        <v>37407.974000000002</v>
+        <v>37407.974</v>
       </c>
       <c r="C50">
-        <v>174.33199999999999</v>
+        <v>174.332</v>
       </c>
       <c r="E50">
         <v>0.187</v>
@@ -2922,19 +2894,19 @@
         <v>0.48</v>
       </c>
       <c r="G50">
-        <v>0.58199999999999996</v>
+        <v>0.582</v>
       </c>
       <c r="H50">
         <v>3784.27</v>
       </c>
       <c r="I50">
-        <v>174.66399999999999</v>
+        <v>174.664</v>
       </c>
       <c r="K50">
-        <v>0.14399999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="L50">
-        <v>0.36199999999999999</v>
+        <v>0.362</v>
       </c>
       <c r="M50">
         <v>1.179</v>
@@ -2952,60 +2924,60 @@
         <v>0.253</v>
       </c>
       <c r="S50">
-        <v>0.93600000000000005</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="T50">
-        <v>31110.434000000001</v>
+        <v>31110.434</v>
       </c>
       <c r="U50">
         <v>180.65</v>
       </c>
       <c r="W50">
-        <v>0.17699999999999999</v>
+        <v>0.177</v>
       </c>
       <c r="X50">
-        <v>0.59599999999999997</v>
+        <v>0.596</v>
       </c>
       <c r="Y50">
-        <v>0.97499999999999998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+        <v>0.975</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>2020</v>
       </c>
       <c r="B51">
-        <v>33873.417000000001</v>
+        <v>33873.417</v>
       </c>
       <c r="C51">
-        <v>174.86099999999999</v>
+        <v>174.861</v>
       </c>
       <c r="E51">
         <v>0.185</v>
       </c>
       <c r="F51">
-        <v>0.48799999999999999</v>
+        <v>0.488</v>
       </c>
       <c r="G51">
-        <v>0.60299999999999998</v>
+        <v>0.603</v>
       </c>
       <c r="H51">
         <v>3434.9</v>
       </c>
       <c r="I51">
-        <v>170.12700000000001</v>
+        <v>170.127</v>
       </c>
       <c r="K51">
-        <v>0.16400000000000001</v>
+        <v>0.164</v>
       </c>
       <c r="L51">
-        <v>0.31900000000000001</v>
+        <v>0.319</v>
       </c>
       <c r="M51">
-        <v>0.66300000000000003</v>
+        <v>0.663</v>
       </c>
       <c r="N51">
-        <v>2116.4899999999998</v>
+        <v>2116.49</v>
       </c>
       <c r="O51">
         <v>144.1</v>
@@ -3017,42 +2989,42 @@
         <v>0.224</v>
       </c>
       <c r="S51">
-        <v>0.82199999999999995</v>
+        <v>0.822</v>
       </c>
       <c r="T51">
-        <v>28322.026999999998</v>
+        <v>28322.027</v>
       </c>
       <c r="U51">
-        <v>186.69200000000001</v>
+        <v>186.692</v>
       </c>
       <c r="W51">
         <v>0.15</v>
       </c>
       <c r="X51">
-        <v>0.63300000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="Y51">
-        <v>1.6040000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1.604</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52">
         <v>2021</v>
       </c>
       <c r="B52">
-        <v>33761.220999999998</v>
+        <v>33761.221</v>
       </c>
       <c r="C52">
-        <v>185.64599999999999</v>
+        <v>185.646</v>
       </c>
       <c r="E52">
         <v>0.15</v>
       </c>
       <c r="F52">
-        <v>0.55300000000000005</v>
+        <v>0.553</v>
       </c>
       <c r="G52">
-        <v>0.59499999999999997</v>
+        <v>0.595</v>
       </c>
       <c r="H52">
         <v>4629.16</v>
@@ -3064,7 +3036,7 @@
         <v>0.18</v>
       </c>
       <c r="L52">
-        <v>0.29099999999999998</v>
+        <v>0.291</v>
       </c>
       <c r="M52">
         <v>1.373</v>
@@ -3073,19 +3045,19 @@
         <v>1639.42</v>
       </c>
       <c r="S52">
-        <v>0.82199999999999995</v>
+        <v>0.822</v>
       </c>
       <c r="T52">
         <v>27492.641</v>
       </c>
       <c r="U52">
-        <v>190.32400000000001</v>
+        <v>190.324</v>
       </c>
       <c r="W52">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="X52">
-        <v>0.61799999999999999</v>
+        <v>0.618</v>
       </c>
       <c r="Y52">
         <v>0.89</v>

--- a/Indicator_4/Real_data/Blue_Shark_SAtl.xlsx
+++ b/Indicator_4/Real_data/Blue_Shark_SAtl.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Parameters" sheetId="1" r:id="rId1"/>
     <sheet name="Time_series" sheetId="2" r:id="rId2"/>
+    <sheet name="B_BMSY" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -471,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>291.8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -498,7 +499,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>291.8</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2079,15 +2080,6 @@
       <c r="H36">
         <v>2523.27</v>
       </c>
-      <c r="I36">
-        <v>164.964</v>
-      </c>
-      <c r="K36">
-        <v>0.222</v>
-      </c>
-      <c r="L36">
-        <v>0.317</v>
-      </c>
       <c r="N36">
         <v>1660.23</v>
       </c>
@@ -2138,15 +2130,6 @@
       <c r="H37">
         <v>2591.33</v>
       </c>
-      <c r="I37">
-        <v>185.782</v>
-      </c>
-      <c r="K37">
-        <v>0.189</v>
-      </c>
-      <c r="L37">
-        <v>0.458</v>
-      </c>
       <c r="N37">
         <v>3281.84</v>
       </c>
@@ -2197,15 +2180,6 @@
       <c r="H38">
         <v>2645.28</v>
       </c>
-      <c r="I38">
-        <v>153.267</v>
-      </c>
-      <c r="K38">
-        <v>0.225</v>
-      </c>
-      <c r="L38">
-        <v>0.195</v>
-      </c>
       <c r="N38">
         <v>3653.3</v>
       </c>
@@ -2247,18 +2221,6 @@
       <c r="H39">
         <v>2012.58</v>
       </c>
-      <c r="I39">
-        <v>214.885</v>
-      </c>
-      <c r="K39">
-        <v>0.165</v>
-      </c>
-      <c r="L39">
-        <v>0.858</v>
-      </c>
-      <c r="M39">
-        <v>0.793</v>
-      </c>
       <c r="N39">
         <v>5521.34</v>
       </c>
@@ -2270,9 +2232,6 @@
       </c>
       <c r="R39">
         <v>0.58</v>
-      </c>
-      <c r="S39">
-        <v>1.019</v>
       </c>
       <c r="T39">
         <v>19307.508</v>
@@ -2312,9 +2271,6 @@
       <c r="H40">
         <v>1273.5</v>
       </c>
-      <c r="M40">
-        <v>0.838</v>
-      </c>
       <c r="N40">
         <v>3768</v>
       </c>
@@ -2326,9 +2282,6 @@
       </c>
       <c r="R40">
         <v>0.299</v>
-      </c>
-      <c r="S40">
-        <v>0.92</v>
       </c>
       <c r="T40">
         <v>21380.072</v>
@@ -2368,18 +2321,6 @@
       <c r="H41">
         <v>1500.5</v>
       </c>
-      <c r="I41">
-        <v>205.528</v>
-      </c>
-      <c r="K41">
-        <v>0.172</v>
-      </c>
-      <c r="L41">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="M41">
-        <v>0.756</v>
-      </c>
       <c r="N41">
         <v>5335.59</v>
       </c>
@@ -2391,9 +2332,6 @@
       </c>
       <c r="R41">
         <v>0.034</v>
-      </c>
-      <c r="S41">
-        <v>1.264</v>
       </c>
       <c r="T41">
         <v>25137.667</v>
@@ -2433,9 +2371,6 @@
       <c r="H42">
         <v>1979.53</v>
       </c>
-      <c r="M42">
-        <v>1.05</v>
-      </c>
       <c r="N42">
         <v>4242.17</v>
       </c>
@@ -2447,9 +2382,6 @@
       </c>
       <c r="R42">
         <v>0.098</v>
-      </c>
-      <c r="S42">
-        <v>1.294</v>
       </c>
       <c r="T42">
         <v>31463.256</v>
@@ -2489,9 +2421,6 @@
       <c r="H43">
         <v>1607.26</v>
       </c>
-      <c r="M43">
-        <v>1.455</v>
-      </c>
       <c r="N43">
         <v>4447.36</v>
       </c>
@@ -2503,9 +2432,6 @@
       </c>
       <c r="R43">
         <v>0.327</v>
-      </c>
-      <c r="S43">
-        <v>1.004</v>
       </c>
       <c r="T43">
         <v>21679.885</v>
@@ -2545,9 +2471,6 @@
       <c r="H44">
         <v>1008.13</v>
       </c>
-      <c r="M44">
-        <v>1.05</v>
-      </c>
       <c r="N44">
         <v>3509.4</v>
       </c>
@@ -2559,9 +2482,6 @@
       </c>
       <c r="R44">
         <v>0.355</v>
-      </c>
-      <c r="S44">
-        <v>1.081</v>
       </c>
       <c r="T44">
         <v>16281.595</v>
@@ -2601,9 +2521,6 @@
       <c r="H45">
         <v>2551.41</v>
       </c>
-      <c r="M45">
-        <v>0.857</v>
-      </c>
       <c r="N45">
         <v>3232</v>
       </c>
@@ -2615,9 +2532,6 @@
       </c>
       <c r="R45">
         <v>0.548</v>
-      </c>
-      <c r="S45">
-        <v>1.157</v>
       </c>
       <c r="T45">
         <v>20469.39</v>
@@ -2657,9 +2571,6 @@
       <c r="H46">
         <v>2420.47</v>
       </c>
-      <c r="M46">
-        <v>1.096</v>
-      </c>
       <c r="N46">
         <v>2277.42</v>
       </c>
@@ -2671,9 +2582,6 @@
       </c>
       <c r="R46">
         <v>0.181</v>
-      </c>
-      <c r="S46">
-        <v>0.89</v>
       </c>
       <c r="T46">
         <v>17800.61</v>
@@ -2713,9 +2621,6 @@
       <c r="H47">
         <v>1334.3</v>
       </c>
-      <c r="M47">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="N47">
         <v>2127.3</v>
       </c>
@@ -2727,9 +2632,6 @@
       </c>
       <c r="R47">
         <v>0.192</v>
-      </c>
-      <c r="S47">
-        <v>0.928</v>
       </c>
       <c r="T47">
         <v>21955.08</v>
@@ -2769,18 +2671,6 @@
       <c r="H48">
         <v>2176.72</v>
       </c>
-      <c r="I48">
-        <v>181.026</v>
-      </c>
-      <c r="K48">
-        <v>0.149</v>
-      </c>
-      <c r="L48">
-        <v>0.41</v>
-      </c>
-      <c r="M48">
-        <v>0.9389999999999999</v>
-      </c>
       <c r="N48">
         <v>3111.65</v>
       </c>
@@ -2792,9 +2682,6 @@
       </c>
       <c r="R48">
         <v>0.471</v>
-      </c>
-      <c r="S48">
-        <v>0.928</v>
       </c>
       <c r="T48">
         <v>23266.52</v>
@@ -2834,18 +2721,6 @@
       <c r="H49">
         <v>3010.73</v>
       </c>
-      <c r="I49">
-        <v>177.627</v>
-      </c>
-      <c r="K49">
-        <v>0.125</v>
-      </c>
-      <c r="L49">
-        <v>0.374</v>
-      </c>
-      <c r="M49">
-        <v>1.142</v>
-      </c>
       <c r="N49">
         <v>3495.36</v>
       </c>
@@ -2857,9 +2732,6 @@
       </c>
       <c r="R49">
         <v>0.614</v>
-      </c>
-      <c r="S49">
-        <v>0.9360000000000001</v>
       </c>
       <c r="T49">
         <v>28007.89</v>
@@ -2899,18 +2771,6 @@
       <c r="H50">
         <v>3784.27</v>
       </c>
-      <c r="I50">
-        <v>174.664</v>
-      </c>
-      <c r="K50">
-        <v>0.144</v>
-      </c>
-      <c r="L50">
-        <v>0.362</v>
-      </c>
-      <c r="M50">
-        <v>1.179</v>
-      </c>
       <c r="N50">
         <v>2513.27</v>
       </c>
@@ -2922,9 +2782,6 @@
       </c>
       <c r="R50">
         <v>0.253</v>
-      </c>
-      <c r="S50">
-        <v>0.9360000000000001</v>
       </c>
       <c r="T50">
         <v>31110.434</v>
@@ -2964,18 +2821,6 @@
       <c r="H51">
         <v>3434.9</v>
       </c>
-      <c r="I51">
-        <v>170.127</v>
-      </c>
-      <c r="K51">
-        <v>0.164</v>
-      </c>
-      <c r="L51">
-        <v>0.319</v>
-      </c>
-      <c r="M51">
-        <v>0.663</v>
-      </c>
       <c r="N51">
         <v>2116.49</v>
       </c>
@@ -2987,9 +2832,6 @@
       </c>
       <c r="R51">
         <v>0.224</v>
-      </c>
-      <c r="S51">
-        <v>0.822</v>
       </c>
       <c r="T51">
         <v>28322.027</v>
@@ -3029,24 +2871,9 @@
       <c r="H52">
         <v>4629.16</v>
       </c>
-      <c r="I52">
-        <v>166.934</v>
-      </c>
-      <c r="K52">
-        <v>0.18</v>
-      </c>
-      <c r="L52">
-        <v>0.291</v>
-      </c>
-      <c r="M52">
-        <v>1.373</v>
-      </c>
       <c r="N52">
         <v>1639.42</v>
       </c>
-      <c r="S52">
-        <v>0.822</v>
-      </c>
       <c r="T52">
         <v>27492.641</v>
       </c>
@@ -3061,6 +2888,696 @@
       </c>
       <c r="Y52">
         <v>0.89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>StDev</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SSB_1971</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>3.476950525384005</v>
+      </c>
+      <c r="C2">
+        <v>0.4589072196155593</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSB_1972</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>3.498644688140677</v>
+      </c>
+      <c r="C3">
+        <v>0.458879700593035</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SSB_1973</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3.515307456279154</v>
+      </c>
+      <c r="C4">
+        <v>0.4588292490517404</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSB_1974</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3.518518008906991</v>
+      </c>
+      <c r="C5">
+        <v>0.4587512784879215</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSB_1975</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3.541822034481335</v>
+      </c>
+      <c r="C6">
+        <v>0.4586595484128405</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSB_1976</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3.568937444675298</v>
+      </c>
+      <c r="C7">
+        <v>0.4505726249936935</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SSB_1977</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>3.592631323068738</v>
+      </c>
+      <c r="C8">
+        <v>0.4314519494934207</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SSB_1978</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>3.574734785420422</v>
+      </c>
+      <c r="C9">
+        <v>0.4042393054198715</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SSB_1979</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>3.547770729850342</v>
+      </c>
+      <c r="C10">
+        <v>0.3750952846154905</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SSB_1980</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>3.514119551806853</v>
+      </c>
+      <c r="C11">
+        <v>0.3478106324330027</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SSB_1981</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>3.470923859451179</v>
+      </c>
+      <c r="C12">
+        <v>0.3239387976939059</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SSB_1982</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>3.46738307855305</v>
+      </c>
+      <c r="C13">
+        <v>0.3037425870633075</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SSB_1983</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>3.419623814962093</v>
+      </c>
+      <c r="C14">
+        <v>0.2869339681054529</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SSB_1984</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>3.437969829978306</v>
+      </c>
+      <c r="C15">
+        <v>0.2731006141328527</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SSB_1985</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>3.42467814209906</v>
+      </c>
+      <c r="C16">
+        <v>0.2618425820181534</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SSB_1986</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>3.424237837738671</v>
+      </c>
+      <c r="C17">
+        <v>0.2528012071677881</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SSB_1987</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>3.394664061532534</v>
+      </c>
+      <c r="C18">
+        <v>0.2456274566460733</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SSB_1988</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>3.386619333947925</v>
+      </c>
+      <c r="C19">
+        <v>0.2398727703858626</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SSB_1989</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>3.311010819562356</v>
+      </c>
+      <c r="C20">
+        <v>0.2352578303085341</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SSB_1990</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>3.189106136283372</v>
+      </c>
+      <c r="C21">
+        <v>0.2314790098655696</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SSB_1991</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>3.050258908136917</v>
+      </c>
+      <c r="C22">
+        <v>0.2283647738165674</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SSB_1992</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2.955946631442318</v>
+      </c>
+      <c r="C23">
+        <v>0.2257807376015337</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SSB_1993</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>2.857015745467388</v>
+      </c>
+      <c r="C24">
+        <v>0.2236590209649087</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SSB_1994</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2.766964330760305</v>
+      </c>
+      <c r="C25">
+        <v>0.2219468791135206</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SSB_1995</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2.599456040654769</v>
+      </c>
+      <c r="C26">
+        <v>0.2185271819144984</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SSB_1996</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2.349331058427471</v>
+      </c>
+      <c r="C27">
+        <v>0.2148501818548738</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SSB_1997</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2.062917658498104</v>
+      </c>
+      <c r="C28">
+        <v>0.2119895794634708</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SSB_1998</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>1.868440726318735</v>
+      </c>
+      <c r="C29">
+        <v>0.2082424058964092</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SSB_1999</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>1.736032949442969</v>
+      </c>
+      <c r="C30">
+        <v>0.2005834032775156</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SSB_2000</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>1.619457783526196</v>
+      </c>
+      <c r="C31">
+        <v>0.1964995803349065</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SSB_2001</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>1.504038416555444</v>
+      </c>
+      <c r="C32">
+        <v>0.1960808325421615</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SSB_2002</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>1.415482202072182</v>
+      </c>
+      <c r="C33">
+        <v>0.1966202053836381</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SSB_2003</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1.3717682347923</v>
+      </c>
+      <c r="C34">
+        <v>0.1949007251262435</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SSB_2004</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>1.338185854305122</v>
+      </c>
+      <c r="C35">
+        <v>0.193047777609606</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SSB_2005</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>1.333888300287574</v>
+      </c>
+      <c r="C36">
+        <v>0.1927120455348093</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SSB_2006</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1.275217744265724</v>
+      </c>
+      <c r="C37">
+        <v>0.1921254317046659</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SSB_2007</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>1.23616366479996</v>
+      </c>
+      <c r="C38">
+        <v>0.1904522751351872</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SSB_2008</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>1.203613247657443</v>
+      </c>
+      <c r="C39">
+        <v>0.1882966183707822</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SSB_2009</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1.182951048245433</v>
+      </c>
+      <c r="C40">
+        <v>0.1877155083451436</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SSB_2010</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1.175429182088786</v>
+      </c>
+      <c r="C41">
+        <v>0.1890355041255602</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SSB_2011</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1.154711944631727</v>
+      </c>
+      <c r="C42">
+        <v>0.1898555709967849</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SSB_2012</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>1.09292256605712</v>
+      </c>
+      <c r="C43">
+        <v>0.193427998770817</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SSB_2013</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>1.150776724410749</v>
+      </c>
+      <c r="C44">
+        <v>0.2000142181616376</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SSB_2014</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1.274731574867794</v>
+      </c>
+      <c r="C45">
+        <v>0.2113924166746931</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SSB_2015</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>1.341676183661956</v>
+      </c>
+      <c r="C46">
+        <v>0.2217817649783747</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SSB_2016</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>1.392985401158551</v>
+      </c>
+      <c r="C47">
+        <v>0.2309089074489407</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SSB_2017</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1.43213579720315</v>
+      </c>
+      <c r="C48">
+        <v>0.2363558393072545</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSB_2018</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1.485921726726934</v>
+      </c>
+      <c r="C49">
+        <v>0.2392852392549683</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SSB_2019</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>1.466204347088258</v>
+      </c>
+      <c r="C50">
+        <v>0.2398851539459985</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SSB_2020</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>1.369364906825176</v>
+      </c>
+      <c r="C51">
+        <v>0.236949332893029</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SSB_2021</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>1.27491962152171</v>
+      </c>
+      <c r="C52">
+        <v>0.2338887589379492</v>
       </c>
     </row>
   </sheetData>
